--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Attaccanti" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$R$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$R$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$P$178</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$P$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$P$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$P$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -645,22 +645,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Svilar</t>
+          <t>Carnesecchi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -668,21 +668,21 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>76.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J3" t="n">
-        <v>6.26</v>
+        <v>6.36</v>
       </c>
       <c r="K3" t="n">
-        <v>5.45</v>
+        <v>5.58</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -703,19 +703,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Martinez Jo.</t>
+          <t>Svilar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
         <v>32</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>76.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>6.26</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -761,37 +761,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vicario</t>
+          <t>Martinez Jo.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>58</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -799,57 +819,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Carnesecchi</t>
+          <t>Vicario</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1a Fascia</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>37</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>35</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -3169,12 +3169,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Padelli</t>
+          <t>Mascardi</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3186,40 +3186,20 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="K51" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3227,12 +3207,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Paleari</t>
+          <t>Padelli</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3250,21 +3230,21 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>40.2</v>
+        <v>53.6</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>6.09</v>
+        <v>6.25</v>
       </c>
       <c r="K52" t="n">
-        <v>4.52</v>
+        <v>5.25</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3273,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -3285,7 +3265,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Siviero</t>
+          <t>Paleari</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3308,7 +3288,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>33.3</v>
+        <v>40.2</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3316,13 +3296,13 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3331,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -3343,12 +3323,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Satalino</t>
+          <t>Siviero</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3401,12 +3381,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mascardi</t>
+          <t>Satalino</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3423,15 +3403,35 @@
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3629,12 +3629,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Montipò</t>
+          <t>Pisseri</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3646,40 +3646,20 @@
       <c r="E61" t="n">
         <v>0</v>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>35</v>
-      </c>
-      <c r="J61" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K61" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>54</v>
-      </c>
-      <c r="O61" t="n">
-        <v>3</v>
-      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3687,12 +3667,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Radunovic</t>
+          <t>Montipò</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3710,33 +3690,33 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>33.3</v>
+        <v>56.1</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
@@ -3745,12 +3725,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pisseri</t>
+          <t>Radunovic</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3767,21 +3747,79 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Bleve</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R63"/>
+  <autoFilter ref="A1:R64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3973,7 +4011,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4025,7 +4063,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4077,7 +4115,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4129,7 +4167,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -4181,7 +4219,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>77.7</v>
+        <v>77.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4269,7 +4307,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -4321,7 +4359,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -4350,22 +4388,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solet</t>
+          <t>Ostigard</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -4381,19 +4419,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>6.18</v>
+        <v>6.13</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>6.52</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -4402,22 +4440,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ostigard</t>
+          <t>Solet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -4425,7 +4463,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>84.3</v>
+        <v>84.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -4433,19 +4471,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J12" t="n">
-        <v>6.13</v>
+        <v>6.18</v>
       </c>
       <c r="K12" t="n">
-        <v>6.52</v>
+        <v>6.4</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -4477,7 +4515,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -4581,7 +4619,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -4685,7 +4723,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -4737,7 +4775,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>77.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -4841,7 +4879,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4945,7 +4983,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -5049,7 +5087,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -5101,7 +5139,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>66.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -5153,7 +5191,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -5205,7 +5243,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>40.2</v>
+        <v>40.5</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -5437,7 +5475,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -5489,7 +5527,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -5541,7 +5579,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -5645,7 +5683,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>74.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -5905,7 +5943,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -6061,7 +6099,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -6113,7 +6151,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>68.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -6165,7 +6203,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>68.2</v>
+        <v>68</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -6217,7 +6255,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>67.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -6269,7 +6307,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -6321,7 +6359,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6373,7 +6411,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -6477,7 +6515,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6558,12 +6596,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Circati</t>
+          <t>Pavard</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6581,7 +6619,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>54.7</v>
+        <v>53.9</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -6589,16 +6627,16 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>5.92</v>
+        <v>6.5</v>
       </c>
       <c r="K55" t="n">
-        <v>5.92</v>
+        <v>6.5</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6610,16 +6648,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pavard</t>
+          <t>Lucumì</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
         <v>18</v>
@@ -6633,24 +6671,24 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>53.9</v>
+        <v>51.4</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>6.5</v>
+        <v>5.88</v>
       </c>
       <c r="K56" t="n">
-        <v>6.5</v>
+        <v>5.89</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6662,22 +6700,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lucumì</t>
+          <t>Zortea</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
@@ -6685,7 +6723,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -6696,16 +6734,16 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>5.88</v>
+        <v>5.86</v>
       </c>
       <c r="K57" t="n">
         <v>5.89</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -6714,22 +6752,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zortea</t>
+          <t>Buongiorno</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
@@ -6737,27 +6775,27 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>5.86</v>
+        <v>5.89</v>
       </c>
       <c r="K58" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -6766,22 +6804,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Buongiorno</t>
+          <t>Idzes</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
@@ -6789,27 +6827,27 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J59" t="n">
-        <v>5.89</v>
+        <v>5.94</v>
       </c>
       <c r="K59" t="n">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
@@ -6818,22 +6856,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Idzes</t>
+          <t>Obert</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
@@ -6841,27 +6879,27 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J60" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="K60" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
@@ -6870,22 +6908,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Obert</t>
+          <t>Ismajli</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
@@ -6893,27 +6931,27 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>48.8</v>
+        <v>47.2</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="K61" t="n">
-        <v>5.82</v>
+        <v>5.9</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
@@ -6922,22 +6960,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ismajli</t>
+          <t>Hien</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
@@ -6945,7 +6983,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6953,19 +6991,19 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="K62" t="n">
-        <v>5.9</v>
+        <v>5.86</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
@@ -6974,22 +7012,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hien</t>
+          <t>Romagnoli</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
@@ -6997,7 +7035,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -7005,16 +7043,16 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J63" t="n">
-        <v>5.91</v>
+        <v>6.03</v>
       </c>
       <c r="K63" t="n">
-        <v>5.86</v>
+        <v>5.92</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7026,22 +7064,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Romagnoli</t>
+          <t>Marcandalli</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
@@ -7049,27 +7087,27 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>6.03</v>
+        <v>5.87</v>
       </c>
       <c r="K64" t="n">
-        <v>5.92</v>
+        <v>5.84</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
@@ -7078,19 +7116,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marcandalli</t>
+          <t>Kamara H.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E65" t="n">
         <v>6</v>
@@ -7101,7 +7139,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -7109,19 +7147,19 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="K65" t="n">
         <v>5.87</v>
       </c>
-      <c r="K65" t="n">
-        <v>5.84</v>
-      </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
@@ -7153,7 +7191,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -7205,7 +7243,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>34.7</v>
+        <v>35</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -7257,7 +7295,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -7309,7 +7347,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -7361,7 +7399,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -7413,7 +7451,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -7465,7 +7503,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -7857,7 +7895,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>70.2</v>
+        <v>70</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -7961,7 +7999,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>63.9</v>
+        <v>63.8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -8013,7 +8051,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -8042,19 +8080,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Zappa</t>
+          <t>Joao Mario</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E86" t="n">
         <v>4</v>
@@ -8065,7 +8103,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -8073,19 +8111,19 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J86" t="n">
-        <v>5.9</v>
+        <v>5.79</v>
       </c>
       <c r="K86" t="n">
-        <v>5.98</v>
+        <v>6</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -8094,19 +8132,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kossounou</t>
+          <t>Zappa</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E87" t="n">
         <v>4</v>
@@ -8117,7 +8155,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>55.5</v>
+        <v>55.9</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -8125,19 +8163,19 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>5.94</v>
+        <v>5.9</v>
       </c>
       <c r="K87" t="n">
-        <v>6.09</v>
+        <v>5.98</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -8146,22 +8184,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>De Winter</t>
+          <t>Kossounou</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -8169,27 +8207,27 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>54.5</v>
+        <v>55.4</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>5.75</v>
+        <v>5.94</v>
       </c>
       <c r="K88" t="n">
-        <v>5.9</v>
+        <v>6.09</v>
       </c>
       <c r="L88" t="n">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -8198,16 +8236,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Parisi</t>
+          <t>De Winter</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
         <v>12</v>
@@ -8221,7 +8259,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -8229,13 +8267,13 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J89" t="n">
-        <v>6.02</v>
+        <v>5.75</v>
       </c>
       <c r="K89" t="n">
-        <v>5.98</v>
+        <v>5.9</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
@@ -8250,19 +8288,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tomori</t>
+          <t>Parisi</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E90" t="n">
         <v>6</v>
@@ -8273,7 +8311,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>48.2</v>
+        <v>54.4</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -8281,16 +8319,16 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J90" t="n">
-        <v>5.97</v>
+        <v>6.02</v>
       </c>
       <c r="K90" t="n">
-        <v>5.88</v>
+        <v>5.98</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
@@ -8302,19 +8340,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kamara H.</t>
+          <t>Tomori</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E91" t="n">
         <v>6</v>
@@ -8325,7 +8363,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>46.3</v>
+        <v>48.4</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -8333,19 +8371,19 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J91" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="K91" t="n">
         <v>5.88</v>
       </c>
-      <c r="K91" t="n">
-        <v>5.87</v>
-      </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
@@ -8377,7 +8415,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -8429,7 +8467,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -8533,7 +8571,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -8585,7 +8623,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -8637,7 +8675,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -8689,7 +8727,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -8741,7 +8779,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -8793,7 +8831,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -8845,7 +8883,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -8897,7 +8935,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -8949,7 +8987,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>35.9</v>
+        <v>36.2</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -9001,7 +9039,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -9053,7 +9091,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -9105,7 +9143,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -9157,7 +9195,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -9209,7 +9247,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -9261,7 +9299,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>33.3</v>
+        <v>33.6</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -9365,7 +9403,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -9417,7 +9455,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -9469,7 +9507,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -9521,7 +9559,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -9573,7 +9611,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -9625,7 +9663,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -10318,22 +10356,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Joao Mario</t>
+          <t>Van Der Brempt</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D135" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E135" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
@@ -10341,7 +10379,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>56.3</v>
+        <v>44.6</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -10352,13 +10390,13 @@
         <v>14</v>
       </c>
       <c r="J135" t="n">
-        <v>5.79</v>
+        <v>5.96</v>
       </c>
       <c r="K135" t="n">
-        <v>6</v>
+        <v>5.96</v>
       </c>
       <c r="L135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
         <v>1</v>
@@ -10370,19 +10408,19 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Van Der Brempt</t>
+          <t>Mazzocchi</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -10393,7 +10431,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>44.7</v>
+        <v>41</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -10401,13 +10439,13 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J136" t="n">
-        <v>5.96</v>
+        <v>5.94</v>
       </c>
       <c r="K136" t="n">
-        <v>5.96</v>
+        <v>5.94</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -10422,19 +10460,19 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mazzocchi</t>
+          <t>Pellegrini Lu.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
@@ -10445,7 +10483,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -10453,19 +10491,19 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J137" t="n">
-        <v>5.94</v>
+        <v>5.85</v>
       </c>
       <c r="K137" t="n">
-        <v>5.94</v>
+        <v>5.81</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
@@ -10474,19 +10512,19 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pellegrini Lu.</t>
+          <t>Carboni F.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E138" t="n">
         <v>2</v>
@@ -10497,7 +10535,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -10505,16 +10543,16 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="K138" t="n">
-        <v>5.81</v>
+        <v>6</v>
       </c>
       <c r="L138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -10526,19 +10564,19 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Carboni F.</t>
+          <t>De Silvestri</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
@@ -10549,7 +10587,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>40.2</v>
+        <v>35.5</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -10557,13 +10595,13 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J139" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="K139" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -10578,19 +10616,19 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>De Silvestri</t>
+          <t>Marianucci</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
@@ -10601,7 +10639,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>35.6</v>
+        <v>29.8</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -10609,19 +10647,19 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J140" t="n">
-        <v>6.05</v>
+        <v>5.73</v>
       </c>
       <c r="K140" t="n">
-        <v>5.95</v>
+        <v>5.73</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
@@ -10630,19 +10668,19 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Marianucci</t>
+          <t>Ebosse</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E141" t="n">
         <v>2</v>
@@ -10653,7 +10691,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -10661,13 +10699,13 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J141" t="n">
-        <v>5.73</v>
+        <v>5.75</v>
       </c>
       <c r="K141" t="n">
-        <v>5.73</v>
+        <v>5.72</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -10682,16 +10720,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Ebosse</t>
+          <t>Patric</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
         <v>4</v>
@@ -10705,27 +10743,27 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>29.1</v>
+        <v>23.7</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J142" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="K142" t="n">
         <v>5.75</v>
       </c>
-      <c r="K142" t="n">
-        <v>5.72</v>
-      </c>
       <c r="L142" t="n">
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
@@ -10734,22 +10772,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Patric</t>
+          <t>Casale</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
@@ -10757,7 +10795,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>23.5</v>
+        <v>20.3</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -10768,10 +10806,10 @@
         <v>10</v>
       </c>
       <c r="J143" t="n">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="K143" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -10786,22 +10824,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Casale</t>
+          <t>Biraghi</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
@@ -10809,7 +10847,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -10817,13 +10855,13 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J144" t="n">
-        <v>5.65</v>
+        <v>5.59</v>
       </c>
       <c r="K144" t="n">
-        <v>5.65</v>
+        <v>5.59</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -10838,19 +10876,19 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Biraghi</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="C145" t="n">
         <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -10861,7 +10899,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>19.8</v>
+        <v>18.4</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -10869,13 +10907,13 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J145" t="n">
-        <v>5.59</v>
+        <v>5.8</v>
       </c>
       <c r="K145" t="n">
-        <v>5.59</v>
+        <v>5.7</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -10890,7 +10928,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Ndaba</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10899,7 +10937,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
         <v>4</v>
@@ -10913,7 +10951,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -10921,13 +10959,13 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J146" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="K146" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -10942,19 +10980,19 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ndaba</t>
+          <t>Sabelli</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E147" t="n">
         <v>2</v>
@@ -10965,7 +11003,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -10973,13 +11011,13 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J147" t="n">
-        <v>5.5</v>
+        <v>5.81</v>
       </c>
       <c r="K147" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -10994,12 +11032,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sabelli</t>
+          <t>Palma</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -11017,7 +11055,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -11025,13 +11063,13 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
-        <v>5.81</v>
+        <v>5.5</v>
       </c>
       <c r="K148" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -11046,7 +11084,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Palma</t>
+          <t>Mlacic</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11055,10 +11093,10 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
         <v>2</v>
@@ -11069,7 +11107,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>16.2</v>
+        <v>14.9</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -11077,13 +11115,13 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J149" t="n">
-        <v>5.5</v>
+        <v>5.83</v>
       </c>
       <c r="K149" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -11098,12 +11136,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Mlacic</t>
+          <t>Rugani</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -11121,7 +11159,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -11129,13 +11167,13 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J150" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="K150" t="n">
-        <v>5.67</v>
+        <v>5.56</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -11150,19 +11188,19 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Rugani</t>
+          <t>Ndiaye</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -11173,7 +11211,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -11181,13 +11219,13 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J151" t="n">
-        <v>5.69</v>
+        <v>5.59</v>
       </c>
       <c r="K151" t="n">
-        <v>5.56</v>
+        <v>5.36</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -11202,19 +11240,19 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ndiaye</t>
+          <t>Otoa</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E152" t="n">
         <v>2</v>
@@ -11225,7 +11263,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -11233,13 +11271,13 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J152" t="n">
-        <v>5.59</v>
+        <v>5.6</v>
       </c>
       <c r="K152" t="n">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -11254,22 +11292,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Otoa</t>
+          <t>Hainaut</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
@@ -11277,7 +11315,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -11285,13 +11323,13 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -11306,22 +11344,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Hainaut</t>
+          <t>Helland</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
@@ -11329,7 +11367,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>12.6</v>
+        <v>11.3</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -11337,13 +11375,13 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="K154" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -11358,51 +11396,35 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Helland</t>
+          <t>Akpoguma</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="G155" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="I155" t="n">
-        <v>6</v>
-      </c>
-      <c r="J155" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K155" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="L155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0</v>
-      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
@@ -11410,12 +11432,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Akpoguma</t>
+          <t>Schingtienne</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -11446,7 +11468,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Schingtienne</t>
+          <t>Sverko</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11482,22 +11504,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sverko</t>
+          <t>Alhassane</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="n">
+        <v>6</v>
+      </c>
+      <c r="E158" t="n">
         <v>3</v>
-      </c>
-      <c r="D158" t="n">
-        <v>7</v>
-      </c>
-      <c r="E158" t="n">
-        <v>4</v>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
@@ -11518,22 +11540,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Alhassane</t>
+          <t>Puczka</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C159" t="n">
         <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
@@ -11554,22 +11576,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Puczka</t>
+          <t>Diawara S.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E160" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
@@ -11590,22 +11612,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Diawara S.</t>
+          <t>Marin R.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
@@ -11626,22 +11648,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Marin R.</t>
+          <t>Franjic</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C162" t="n">
         <v>2</v>
       </c>
       <c r="D162" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
@@ -11662,7 +11684,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Franjic</t>
+          <t>Sagrado</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11698,19 +11720,19 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sagrado</t>
+          <t>Aurelio</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C164" t="n">
         <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E164" t="n">
         <v>2</v>
@@ -11734,19 +11756,19 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Aurelio</t>
+          <t>Oyono J.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E165" t="n">
         <v>2</v>
@@ -11770,7 +11792,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Oyono J.</t>
+          <t>Corrado</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11806,22 +11828,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Corrado</t>
+          <t>Matturro</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
@@ -11937,7 +11959,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -12194,12 +12216,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Matturro</t>
+          <t>Antov</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -12230,22 +12252,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Antov</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
@@ -12266,12 +12288,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Omar Fayed</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -12311,7 +12333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P179"/>
+  <dimension ref="A1:P180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13441,50 +13463,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rowe</t>
+          <t>Zambo Anguissa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
+        <v>27</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>1a Fascia</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>18</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>1a Fascia</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>28</v>
-      </c>
       <c r="J22" t="n">
-        <v>6.2</v>
+        <v>6.17</v>
       </c>
       <c r="K22" t="n">
-        <v>6.59</v>
+        <v>6.86</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -13493,22 +13515,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zambo Anguissa</t>
+          <t>Thorstvedt</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E23" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -13516,7 +13538,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13524,19 +13546,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
       <c r="K23" t="n">
-        <v>6.86</v>
+        <v>6.48</v>
       </c>
       <c r="L23" t="n">
         <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -13545,22 +13567,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thorstvedt</t>
+          <t>Gudmundsson A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -13568,7 +13590,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>75.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13576,16 +13598,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J24" t="n">
-        <v>6.15</v>
+        <v>5.88</v>
       </c>
       <c r="K24" t="n">
-        <v>6.48</v>
+        <v>6.34</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
@@ -13597,22 +13619,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gudmundsson A.</t>
+          <t>Saelemaekers</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -13620,7 +13642,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>73.8</v>
+        <v>73</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13628,16 +13650,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J25" t="n">
-        <v>5.88</v>
+        <v>6.14</v>
       </c>
       <c r="K25" t="n">
-        <v>6.34</v>
+        <v>6.41</v>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
         <v>3</v>
@@ -13649,22 +13671,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Saelemaekers</t>
+          <t>Konè M.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -13672,7 +13694,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>73</v>
+        <v>70.7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13680,16 +13702,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>6.14</v>
+        <v>6.26</v>
       </c>
       <c r="K26" t="n">
-        <v>6.41</v>
+        <v>6.53</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
         <v>3</v>
@@ -13701,22 +13723,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Konè M.</t>
+          <t>Thuram K.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -13724,7 +13746,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>70.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13732,19 +13754,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J27" t="n">
-        <v>6.26</v>
+        <v>6.1</v>
       </c>
       <c r="K27" t="n">
-        <v>6.53</v>
+        <v>6.4</v>
       </c>
       <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="n">
         <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -13753,22 +13775,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Thuram K.</t>
+          <t>Taylor K.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -13776,21 +13798,21 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>69.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>6.1</v>
+        <v>6.06</v>
       </c>
       <c r="K28" t="n">
-        <v>6.4</v>
+        <v>6.56</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -13805,22 +13827,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Taylor K.</t>
+          <t>Politano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -13836,19 +13858,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J29" t="n">
-        <v>6.06</v>
+        <v>6.09</v>
       </c>
       <c r="K29" t="n">
-        <v>6.56</v>
+        <v>6.36</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -13857,22 +13879,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Politano</t>
+          <t>Ederson D.S.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -13880,7 +13902,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>69.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -13888,19 +13910,19 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>6.09</v>
+        <v>6.25</v>
       </c>
       <c r="K30" t="n">
-        <v>6.36</v>
+        <v>6.43</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -13909,7 +13931,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ederson D.S.</t>
+          <t>Samardzic</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13921,10 +13943,10 @@
         <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -13932,7 +13954,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>61.9</v>
+        <v>58.6</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -13940,19 +13962,19 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>6.25</v>
+        <v>5.93</v>
       </c>
       <c r="K31" t="n">
-        <v>6.43</v>
+        <v>6.29</v>
       </c>
       <c r="L31" t="n">
         <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -13961,22 +13983,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Samardzic</t>
+          <t>Zaccagni</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="E32" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -13984,7 +14006,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>58.6</v>
+        <v>43.9</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -13992,19 +14014,19 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>5.93</v>
+        <v>5.88</v>
       </c>
       <c r="K32" t="n">
-        <v>6.29</v>
+        <v>5.96</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -14013,7 +14035,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Zaccagni</t>
+          <t>Frattesi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14022,13 +14044,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="E33" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -14036,7 +14058,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>43.9</v>
+        <v>23</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14044,16 +14066,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J33" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="K33" t="n">
-        <v>5.96</v>
+        <v>5.89</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -14065,19 +14087,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Frattesi</t>
+          <t>Alajbegovic</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E34" t="n">
         <v>28</v>
@@ -14087,29 +14109,13 @@
           <t>1a Fascia</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>23</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>14</v>
-      </c>
-      <c r="J34" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="K34" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -14117,22 +14123,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alajbegovic</t>
+          <t>Mastantuono</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -14153,22 +14159,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mastantuono</t>
+          <t>Moreira</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>12</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E36" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -14397,50 +14403,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pellegrini Lo.</t>
+          <t>Rowe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
+        <v>37</v>
+      </c>
+      <c r="E41" t="n">
+        <v>18</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
         <v>28</v>
       </c>
-      <c r="E41" t="n">
-        <v>14</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>24</v>
-      </c>
       <c r="J41" t="n">
-        <v>6.04</v>
+        <v>6.2</v>
       </c>
       <c r="K41" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -14449,22 +14455,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bernardeschi</t>
+          <t>Pellegrini Lo.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
@@ -14472,7 +14478,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>74.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14486,7 +14492,7 @@
         <v>6.04</v>
       </c>
       <c r="K42" t="n">
-        <v>6.56</v>
+        <v>6.58</v>
       </c>
       <c r="L42" t="n">
         <v>4</v>
@@ -14501,7 +14507,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Odgaard</t>
+          <t>Bernardeschi</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14510,13 +14516,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
@@ -14524,7 +14530,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14532,19 +14538,19 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>5.91</v>
+        <v>6.04</v>
       </c>
       <c r="K43" t="n">
-        <v>6.61</v>
+        <v>6.56</v>
       </c>
       <c r="L43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -14553,47 +14559,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mkhitaryan</t>
+          <t>Odgaard</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>22</v>
+      </c>
+      <c r="E44" t="n">
+        <v>11</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>22</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="K44" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="L44" t="n">
         <v>5</v>
-      </c>
-      <c r="D44" t="n">
-        <v>19</v>
-      </c>
-      <c r="E44" t="n">
-        <v>10</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>73</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>28</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="K44" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="L44" t="n">
-        <v>4</v>
       </c>
       <c r="M44" t="n">
         <v>1</v>
@@ -14605,22 +14611,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cambiaghi</t>
+          <t>Mkhitaryan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
@@ -14628,27 +14634,27 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>71.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>5.98</v>
+        <v>6.21</v>
       </c>
       <c r="K45" t="n">
-        <v>6.42</v>
+        <v>6.59</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -14657,22 +14663,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bernabè</t>
+          <t>Cambiaghi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E46" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
@@ -14680,7 +14686,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>69.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14688,19 +14694,19 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>6.17</v>
+        <v>5.98</v>
       </c>
       <c r="K46" t="n">
-        <v>6.48</v>
+        <v>6.42</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -14709,22 +14715,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Zalewski</t>
+          <t>Bernabè</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
@@ -14732,7 +14738,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14740,19 +14746,19 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>6.1</v>
+        <v>6.17</v>
       </c>
       <c r="K47" t="n">
-        <v>6.4</v>
+        <v>6.48</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -14761,30 +14767,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Casadei</t>
+          <t>Zalewski</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="C48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" t="n">
+        <v>21</v>
+      </c>
+      <c r="E48" t="n">
         <v>10</v>
       </c>
-      <c r="D48" t="n">
-        <v>37</v>
-      </c>
-      <c r="E48" t="n">
-        <v>18</v>
-      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>69.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14792,19 +14798,19 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J48" t="n">
-        <v>5.97</v>
+        <v>6.1</v>
       </c>
       <c r="K48" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="L48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -14813,22 +14819,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Volpato</t>
+          <t>Casadei</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
@@ -14844,19 +14850,19 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>6.14</v>
+        <v>5.97</v>
       </c>
       <c r="K49" t="n">
-        <v>6.52</v>
+        <v>6.45</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -14865,22 +14871,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caqueret</t>
+          <t>Volpato</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
@@ -14888,7 +14894,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>67.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14896,13 +14902,13 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>6.11</v>
+        <v>6.14</v>
       </c>
       <c r="K50" t="n">
-        <v>6.41</v>
+        <v>6.52</v>
       </c>
       <c r="L50" t="n">
         <v>2</v>
@@ -14917,22 +14923,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pasalic</t>
+          <t>Caqueret</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E51" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
@@ -14940,7 +14946,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>67.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14948,19 +14954,19 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>5.94</v>
+        <v>6.11</v>
       </c>
       <c r="K51" t="n">
-        <v>6.27</v>
+        <v>6.41</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -14969,7 +14975,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gaetano</t>
+          <t>Pasalic</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -14978,13 +14984,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D52" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
@@ -15000,19 +15006,19 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J52" t="n">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="K52" t="n">
-        <v>6.31</v>
+        <v>6.27</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -15021,22 +15027,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Gaetano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
@@ -15044,7 +15050,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>65.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15052,19 +15058,19 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>6.09</v>
+        <v>6.06</v>
       </c>
       <c r="K53" t="n">
-        <v>6.43</v>
+        <v>6.31</v>
       </c>
       <c r="L53" t="n">
         <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -15073,22 +15079,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cancellieri</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
@@ -15096,7 +15102,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>63.7</v>
+        <v>65.5</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15104,19 +15110,19 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="K54" t="n">
-        <v>6.29</v>
+        <v>6.43</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -15125,22 +15131,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fagioli</t>
+          <t>Cancellieri</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E55" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
@@ -15148,7 +15154,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>63.4</v>
+        <v>63.7</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15156,19 +15162,19 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>6.03</v>
+        <v>5.93</v>
       </c>
       <c r="K55" t="n">
-        <v>6.23</v>
+        <v>6.29</v>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -15177,22 +15183,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cristante</t>
+          <t>Fagioli</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
@@ -15200,7 +15206,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>59.6</v>
+        <v>63.4</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15208,19 +15214,19 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J56" t="n">
-        <v>6.11</v>
+        <v>6.03</v>
       </c>
       <c r="K56" t="n">
-        <v>6.22</v>
+        <v>6.23</v>
       </c>
       <c r="L56" t="n">
         <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -15229,22 +15235,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sucic P.</t>
+          <t>Cristante</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
@@ -15252,7 +15258,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>58.9</v>
+        <v>59.6</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15260,19 +15266,19 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J57" t="n">
-        <v>6.07</v>
+        <v>6.11</v>
       </c>
       <c r="K57" t="n">
-        <v>6.27</v>
+        <v>6.22</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -15281,22 +15287,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fofana Y.</t>
+          <t>Sucic P.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
@@ -15312,19 +15318,19 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>5.85</v>
+        <v>6.07</v>
       </c>
       <c r="K58" t="n">
-        <v>6.06</v>
+        <v>6.27</v>
       </c>
       <c r="L58" t="n">
         <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -15333,22 +15339,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Locatelli</t>
+          <t>Fofana Y.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E59" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
@@ -15356,27 +15362,27 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>53.6</v>
+        <v>58.9</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J59" t="n">
-        <v>6.26</v>
+        <v>5.85</v>
       </c>
       <c r="K59" t="n">
-        <v>6.19</v>
+        <v>6.06</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
@@ -15385,22 +15391,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Baldanzi</t>
+          <t>Locatelli</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
@@ -15408,7 +15414,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>53.2</v>
+        <v>53.6</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15416,13 +15422,13 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J60" t="n">
-        <v>6.15</v>
+        <v>6.26</v>
       </c>
       <c r="K60" t="n">
-        <v>6.38</v>
+        <v>6.19</v>
       </c>
       <c r="L60" t="n">
         <v>1</v>
@@ -15437,22 +15443,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ndour</t>
+          <t>Baldanzi</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D61" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
@@ -15460,27 +15466,27 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>52.2</v>
+        <v>53.2</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>5.8</v>
+        <v>6.15</v>
       </c>
       <c r="K61" t="n">
-        <v>6.07</v>
+        <v>6.38</v>
       </c>
       <c r="L61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
@@ -15489,22 +15495,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Vergara</t>
+          <t>Ndour</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E62" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
@@ -15512,24 +15518,24 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>48.1</v>
+        <v>52.2</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J62" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="K62" t="n">
-        <v>6.5</v>
+        <v>6.07</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -15541,22 +15547,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Diouf</t>
+          <t>Vergara</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E63" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
@@ -15564,7 +15570,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>47.5</v>
+        <v>48.1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15572,13 +15578,13 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="K63" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="L63" t="n">
         <v>1</v>
@@ -15593,50 +15599,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>El Aynaoui</t>
+          <t>Diouf</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
+        <v>37</v>
+      </c>
+      <c r="E64" t="n">
         <v>18</v>
       </c>
-      <c r="E64" t="n">
-        <v>9</v>
-      </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>5.98</v>
+        <v>6.15</v>
       </c>
       <c r="K64" t="n">
-        <v>6.1</v>
+        <v>6.45</v>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
@@ -17265,22 +17271,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Miretti</t>
+          <t>El Aynaoui</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E98" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
@@ -17288,27 +17294,27 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J98" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
       <c r="K98" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
@@ -17317,44 +17323,44 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Matic</t>
+          <t>Miretti</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
+        <v>11</v>
+      </c>
+      <c r="E99" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
         <v>15</v>
       </c>
-      <c r="E99" t="n">
-        <v>8</v>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>34</v>
-      </c>
       <c r="J99" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
       <c r="K99" t="n">
-        <v>5.96</v>
+        <v>6.2</v>
       </c>
       <c r="L99" t="n">
         <v>1</v>
@@ -17369,22 +17375,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Njie</t>
+          <t>Matic</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D100" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
@@ -17392,7 +17398,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>44.3</v>
+        <v>44.6</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -17400,13 +17406,13 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J100" t="n">
-        <v>5.8</v>
+        <v>5.96</v>
       </c>
       <c r="K100" t="n">
-        <v>6.15</v>
+        <v>5.96</v>
       </c>
       <c r="L100" t="n">
         <v>1</v>
@@ -17421,19 +17427,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Adopo</t>
+          <t>Njie</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E101" t="n">
         <v>6</v>
@@ -17444,7 +17450,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17452,13 +17458,13 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="K101" t="n">
-        <v>5.88</v>
+        <v>6.15</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
@@ -17473,19 +17479,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sorensen O.</t>
+          <t>Adopo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E102" t="n">
         <v>6</v>
@@ -17496,7 +17502,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>42.8</v>
+        <v>44.2</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17504,13 +17510,13 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J102" t="n">
-        <v>5.85</v>
+        <v>5.83</v>
       </c>
       <c r="K102" t="n">
-        <v>5.95</v>
+        <v>5.88</v>
       </c>
       <c r="L102" t="n">
         <v>1</v>
@@ -17525,12 +17531,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Dominguez B.</t>
+          <t>Sorensen O.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -17548,7 +17554,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>39.9</v>
+        <v>42.8</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17556,19 +17562,19 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J103" t="n">
-        <v>5.83</v>
+        <v>5.85</v>
       </c>
       <c r="K103" t="n">
-        <v>6.04</v>
+        <v>5.95</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
@@ -17577,22 +17583,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Piotrowski</t>
+          <t>Dominguez B.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E104" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -17600,7 +17606,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>38</v>
+        <v>39.9</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17608,19 +17614,19 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J104" t="n">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="K104" t="n">
-        <v>5.95</v>
+        <v>6.04</v>
       </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
@@ -17629,7 +17635,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Miller L.</t>
+          <t>Piotrowski</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -17638,13 +17644,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D105" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
@@ -17652,7 +17658,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>34.6</v>
+        <v>38</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17660,19 +17666,19 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J105" t="n">
-        <v>5.92</v>
+        <v>5.88</v>
       </c>
       <c r="K105" t="n">
         <v>5.95</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
@@ -17681,19 +17687,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Zerbin</t>
+          <t>Miller L.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E106" t="n">
         <v>6</v>
@@ -17704,7 +17710,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17712,13 +17718,13 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J106" t="n">
-        <v>5.76</v>
+        <v>5.92</v>
       </c>
       <c r="K106" t="n">
-        <v>5.79</v>
+        <v>5.95</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -17733,22 +17739,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Almqvist</t>
+          <t>Zerbin</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E107" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
@@ -17764,19 +17770,19 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J107" t="n">
-        <v>5.94</v>
+        <v>5.76</v>
       </c>
       <c r="K107" t="n">
-        <v>6.06</v>
+        <v>5.79</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
@@ -17785,22 +17791,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dele-Bashiru</t>
+          <t>Almqvist</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
@@ -17808,7 +17814,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>30.6</v>
+        <v>33.8</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17816,19 +17822,19 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J108" t="n">
-        <v>5.69</v>
+        <v>5.94</v>
       </c>
       <c r="K108" t="n">
-        <v>5.83</v>
+        <v>6.06</v>
       </c>
       <c r="L108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
@@ -17837,22 +17843,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bakola</t>
+          <t>Dele-Bashiru</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>5</v>
       </c>
       <c r="D109" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
@@ -17860,7 +17866,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>29</v>
+        <v>30.6</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17868,16 +17874,16 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J109" t="n">
-        <v>6.17</v>
+        <v>5.69</v>
       </c>
       <c r="K109" t="n">
-        <v>6.17</v>
+        <v>5.83</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -17889,22 +17895,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Gineitis</t>
+          <t>Bakola</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
@@ -17912,7 +17918,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17920,19 +17926,19 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
-        <v>5.87</v>
+        <v>6.17</v>
       </c>
       <c r="K110" t="n">
-        <v>5.81</v>
+        <v>6.17</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
@@ -17941,44 +17947,44 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Akinsanmiro</t>
+          <t>Gineitis</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C111" t="n">
+        <v>5</v>
+      </c>
+      <c r="D111" t="n">
+        <v>13</v>
+      </c>
+      <c r="E111" t="n">
         <v>6</v>
       </c>
-      <c r="D111" t="n">
-        <v>16</v>
-      </c>
-      <c r="E111" t="n">
-        <v>8</v>
-      </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>27.6</v>
+        <v>27.9</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J111" t="n">
-        <v>5.8</v>
+        <v>5.87</v>
       </c>
       <c r="K111" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -17993,22 +17999,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jashari</t>
+          <t>Akinsanmiro</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D112" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E112" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
@@ -18016,21 +18022,21 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>25.2</v>
+        <v>27.6</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J112" t="n">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="K112" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -18045,22 +18051,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sohm</t>
+          <t>Jashari</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
@@ -18068,21 +18074,21 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>22.8</v>
+        <v>25.2</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J113" t="n">
-        <v>5.65</v>
+        <v>5.71</v>
       </c>
       <c r="K113" t="n">
-        <v>5.62</v>
+        <v>5.79</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -18097,12 +18103,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Koopmeiners</t>
+          <t>Sohm</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -18120,7 +18126,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>19.2</v>
+        <v>22.8</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -18128,19 +18134,19 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J114" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="K114" t="n">
-        <v>5.55</v>
+        <v>5.62</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
@@ -18149,22 +18155,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Rovella</t>
+          <t>Koopmeiners</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
@@ -18172,7 +18178,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>17.7</v>
+        <v>19.2</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -18180,19 +18186,19 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J115" t="n">
-        <v>5.73</v>
+        <v>5.64</v>
       </c>
       <c r="K115" t="n">
-        <v>5.64</v>
+        <v>5.55</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
@@ -18201,50 +18207,50 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ngom</t>
+          <t>Rovella</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D116" t="n">
+        <v>16</v>
+      </c>
+      <c r="E116" t="n">
+        <v>8</v>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
         <v>11</v>
       </c>
-      <c r="E116" t="n">
-        <v>6</v>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="I116" t="n">
-        <v>13</v>
-      </c>
       <c r="J116" t="n">
-        <v>5.69</v>
+        <v>5.73</v>
       </c>
       <c r="K116" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
@@ -18253,12 +18259,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Amorim</t>
+          <t>Ngom</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -18276,21 +18282,21 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J117" t="n">
-        <v>5.72</v>
+        <v>5.69</v>
       </c>
       <c r="K117" t="n">
-        <v>5.67</v>
+        <v>5.65</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -18305,16 +18311,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Chukwueze</t>
+          <t>Amorim</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
         <v>11</v>
@@ -18328,7 +18334,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>11.1</v>
+        <v>13.6</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -18336,13 +18342,13 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J118" t="n">
-        <v>5.5</v>
+        <v>5.72</v>
       </c>
       <c r="K118" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -18357,19 +18363,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Douglas Luiz</t>
+          <t>Chukwueze</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E119" t="n">
         <v>6</v>
@@ -18380,7 +18386,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -18388,13 +18394,13 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -18409,35 +18415,51 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Pessina</t>
+          <t>Douglas Luiz</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D120" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E120" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
+      <c r="G120" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
@@ -18445,22 +18467,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sow</t>
+          <t>Pessina</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>7</v>
       </c>
       <c r="D121" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
@@ -18481,16 +18503,16 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Winks</t>
+          <t>Sow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D122" t="n">
         <v>14</v>
@@ -18517,22 +18539,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Amondarain</t>
+          <t>Winks</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
@@ -18553,12 +18575,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Romano</t>
+          <t>Amondarain</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -18589,22 +18611,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Milla</t>
+          <t>Romano</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>5</v>
       </c>
       <c r="D125" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
@@ -18625,12 +18647,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Meichtry</t>
+          <t>Milla</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -18661,7 +18683,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Traorè Hj.</t>
+          <t>Meichtry</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -18673,10 +18695,10 @@
         <v>5</v>
       </c>
       <c r="D127" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
@@ -18697,22 +18719,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Busio</t>
+          <t>Traorè Hj.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>5</v>
       </c>
       <c r="D128" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
@@ -18733,7 +18755,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Perez K.</t>
+          <t>Busio</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -18769,12 +18791,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Grillitsch</t>
+          <t>Perez K.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -18805,7 +18827,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cichella</t>
+          <t>Grillitsch</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -18814,13 +18836,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
@@ -18841,7 +18863,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Koutsoupias</t>
+          <t>Cichella</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -18853,7 +18875,7 @@
         <v>4</v>
       </c>
       <c r="D132" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E132" t="n">
         <v>6</v>
@@ -18877,19 +18899,19 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fitz-Jim</t>
+          <t>Koutsoupias</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>4</v>
       </c>
       <c r="D133" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E133" t="n">
         <v>6</v>
@@ -18913,19 +18935,19 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Diallo O.</t>
+          <t>Fitz-Jim</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D134" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E134" t="n">
         <v>6</v>
@@ -18949,51 +18971,35 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Messias</t>
+          <t>Diallo O.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E135" t="n">
-        <v>4</v>
-      </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="I135" t="n">
-        <v>19</v>
-      </c>
-      <c r="J135" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="K135" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="L135" t="n">
-        <v>3</v>
-      </c>
-      <c r="M135" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
@@ -19001,19 +19007,19 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Brescianini</t>
+          <t>Messias</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E136" t="n">
         <v>4</v>
@@ -19024,7 +19030,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>55.2</v>
+        <v>71.2</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -19032,16 +19038,16 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J136" t="n">
-        <v>5.97</v>
+        <v>6.18</v>
       </c>
       <c r="K136" t="n">
-        <v>6.31</v>
+        <v>6.68</v>
       </c>
       <c r="L136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M136" t="n">
         <v>1</v>
@@ -19053,22 +19059,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fadera</t>
+          <t>Brescianini</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
@@ -19076,7 +19082,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>52.1</v>
+        <v>55.2</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -19084,13 +19090,13 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J137" t="n">
-        <v>5.92</v>
+        <v>5.97</v>
       </c>
       <c r="K137" t="n">
-        <v>6.15</v>
+        <v>6.31</v>
       </c>
       <c r="L137" t="n">
         <v>2</v>
@@ -19105,22 +19111,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Fabbian</t>
+          <t>Fadera</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E138" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
@@ -19128,7 +19134,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>43.8</v>
+        <v>52.1</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -19136,19 +19142,19 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J138" t="n">
-        <v>5.8</v>
+        <v>5.92</v>
       </c>
       <c r="K138" t="n">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
@@ -19157,22 +19163,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ilkhan</t>
+          <t>Fabbian</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
@@ -19180,7 +19186,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>43</v>
+        <v>43.8</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -19188,19 +19194,19 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J139" t="n">
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="K139" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="L139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
@@ -19209,22 +19215,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Gilmour</t>
+          <t>Ilkhan</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
@@ -19232,7 +19238,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>42.1</v>
+        <v>43</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -19240,19 +19246,19 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J140" t="n">
-        <v>6.08</v>
+        <v>5.82</v>
       </c>
       <c r="K140" t="n">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
@@ -19261,22 +19267,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Musah</t>
+          <t>Gilmour</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
@@ -19284,7 +19290,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>37.9</v>
+        <v>42.1</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -19292,13 +19298,13 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J141" t="n">
-        <v>5.94</v>
+        <v>6.08</v>
       </c>
       <c r="K141" t="n">
-        <v>6.09</v>
+        <v>6.27</v>
       </c>
       <c r="L141" t="n">
         <v>1</v>
@@ -19313,22 +19319,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Prati</t>
+          <t>Musah</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
@@ -19336,7 +19342,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>35.2</v>
+        <v>37.9</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -19344,13 +19350,13 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J142" t="n">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="K142" t="n">
-        <v>5.88</v>
+        <v>6.09</v>
       </c>
       <c r="L142" t="n">
         <v>1</v>
@@ -19365,7 +19371,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Deiola</t>
+          <t>Prati</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -19374,10 +19380,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D143" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E143" t="n">
         <v>4</v>
@@ -19388,27 +19394,27 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>29.8</v>
+        <v>35.2</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J143" t="n">
-        <v>5.98</v>
+        <v>5.88</v>
       </c>
       <c r="K143" t="n">
-        <v>5.95</v>
+        <v>5.88</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
@@ -19417,22 +19423,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Lipani</t>
+          <t>Deiola</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
@@ -19440,21 +19446,21 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>29.1</v>
+        <v>29.8</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J144" t="n">
-        <v>5.93</v>
+        <v>5.98</v>
       </c>
       <c r="K144" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -19469,12 +19475,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ordonez C.</t>
+          <t>Lipani</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -19492,7 +19498,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>28.4</v>
+        <v>29.1</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -19503,16 +19509,16 @@
         <v>21</v>
       </c>
       <c r="J145" t="n">
-        <v>5.79</v>
+        <v>5.93</v>
       </c>
       <c r="K145" t="n">
-        <v>5.81</v>
+        <v>5.9</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
@@ -19521,16 +19527,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Belahyane</t>
+          <t>Ordonez C.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" t="n">
         <v>5</v>
@@ -19552,19 +19558,19 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J146" t="n">
-        <v>5.77</v>
+        <v>5.79</v>
       </c>
       <c r="K146" t="n">
-        <v>5.82</v>
+        <v>5.81</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
@@ -19573,19 +19579,19 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Masini</t>
+          <t>Belahyane</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E147" t="n">
         <v>2</v>
@@ -19596,7 +19602,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -19604,19 +19610,19 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J147" t="n">
-        <v>5.98</v>
+        <v>5.77</v>
       </c>
       <c r="K147" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
@@ -19625,22 +19631,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sulemana I.</t>
+          <t>Masini</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
@@ -19648,27 +19654,27 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>26.9</v>
+        <v>28.3</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J148" t="n">
-        <v>5.69</v>
+        <v>5.98</v>
       </c>
       <c r="K148" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="L148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
@@ -19677,22 +19683,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Maleh</t>
+          <t>Sulemana I.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
@@ -19700,7 +19706,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>25.4</v>
+        <v>26.9</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -19708,13 +19714,13 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J149" t="n">
         <v>5.69</v>
       </c>
       <c r="K149" t="n">
-        <v>5.71</v>
+        <v>5.78</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
@@ -19729,22 +19735,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Venturino</t>
+          <t>Maleh</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
@@ -19752,7 +19758,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>19.5</v>
+        <v>25.4</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19760,16 +19766,16 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J150" t="n">
-        <v>5.86</v>
+        <v>5.69</v>
       </c>
       <c r="K150" t="n">
-        <v>5.86</v>
+        <v>5.71</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -19781,22 +19787,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ilic</t>
+          <t>Venturino</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
@@ -19804,7 +19810,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>18.4</v>
+        <v>19.5</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19812,13 +19818,13 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J151" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="K151" t="n">
-        <v>5.88</v>
+        <v>5.86</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -19833,19 +19839,19 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Boloca</t>
+          <t>Ilic</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E152" t="n">
         <v>2</v>
@@ -19856,7 +19862,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>15.3</v>
+        <v>18.4</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19864,13 +19870,13 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J152" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="K152" t="n">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -19885,19 +19891,19 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Anjorin</t>
+          <t>Boloca</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -19908,7 +19914,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19916,13 +19922,13 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
-        <v>5.78</v>
+        <v>5.75</v>
       </c>
       <c r="K153" t="n">
-        <v>5.72</v>
+        <v>5.75</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -19937,12 +19943,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Zarraga</t>
+          <t>Anjorin</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -19968,13 +19974,13 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J154" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="K154" t="n">
-        <v>5.7</v>
+        <v>5.72</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -19989,19 +19995,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Aboukhlal</t>
+          <t>Zarraga</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -20012,7 +20018,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -20020,13 +20026,13 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J155" t="n">
-        <v>5.77</v>
+        <v>5.75</v>
       </c>
       <c r="K155" t="n">
-        <v>5.64</v>
+        <v>5.7</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -20041,22 +20047,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Helgason</t>
+          <t>Aboukhlal</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
@@ -20064,7 +20070,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -20072,13 +20078,13 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J156" t="n">
-        <v>5.62</v>
+        <v>5.77</v>
       </c>
       <c r="K156" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -20093,19 +20099,19 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Fini</t>
+          <t>Helgason</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E157" t="n">
         <v>4</v>
@@ -20116,7 +20122,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -20124,13 +20130,13 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J157" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="K157" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -20145,22 +20151,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Gorter</t>
+          <t>Fini</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
@@ -20197,22 +20203,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Cissè A.</t>
+          <t>Gorter</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
         <v>3</v>
       </c>
-      <c r="D159" t="n">
-        <v>8</v>
-      </c>
       <c r="E159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
@@ -20220,7 +20226,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -20228,13 +20234,13 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -20249,22 +20255,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>El Azzouzi O.</t>
+          <t>Cissè A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
+        <v>8</v>
+      </c>
+      <c r="E160" t="n">
         <v>4</v>
-      </c>
-      <c r="E160" t="n">
-        <v>2</v>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
@@ -20301,19 +20307,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Przyborek</t>
+          <t>El Azzouzi O.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E161" t="n">
         <v>2</v>
@@ -20353,35 +20359,51 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Gelli F.</t>
+          <t>Przyborek</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E162" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
+      <c r="G162" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
@@ -20389,22 +20411,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Stankovic A.</t>
+          <t>Gelli F.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C163" t="n">
         <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
@@ -20425,22 +20447,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Colombo L.</t>
+          <t>Stankovic A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="C164" t="n">
         <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
@@ -20461,22 +20483,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Hasa</t>
+          <t>Colombo L.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
@@ -20497,22 +20519,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ciurria</t>
+          <t>Hasa</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>2</v>
       </c>
       <c r="D166" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
@@ -20533,12 +20555,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Chakvetadze</t>
+          <t>Ciurria</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -20569,22 +20591,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Chakvetadze</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C168" t="n">
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
@@ -20605,19 +20627,19 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>El Azzouzi A.</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E169" t="n">
         <v>2</v>
@@ -20641,7 +20663,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Kone B.</t>
+          <t>El Azzouzi A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -20677,51 +20699,35 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Iannoni</t>
+          <t>Kone B.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C171" t="n">
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="G171" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="I171" t="n">
-        <v>5</v>
-      </c>
-      <c r="J171" t="n">
-        <v>6</v>
-      </c>
-      <c r="K171" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L171" t="n">
-        <v>1</v>
-      </c>
-      <c r="M171" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
@@ -20729,22 +20735,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Cremaschi</t>
+          <t>Iannoni</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
@@ -20752,7 +20758,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>23.9</v>
+        <v>50.3</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -20760,16 +20766,16 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J172" t="n">
         <v>6</v>
       </c>
       <c r="K172" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
@@ -20781,22 +20787,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Liteta</t>
+          <t>Cremaschi</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C173" t="n">
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
@@ -20804,21 +20810,21 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>15.7</v>
+        <v>23.9</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="K173" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -20833,22 +20839,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Kaba</t>
+          <t>Liteta</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
@@ -20864,13 +20870,13 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J174" t="n">
-        <v>5.77</v>
+        <v>5.75</v>
       </c>
       <c r="K174" t="n">
-        <v>5.73</v>
+        <v>5.75</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -20885,7 +20891,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Fofana Sa.</t>
+          <t>Kaba</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -20897,10 +20903,10 @@
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
@@ -20908,7 +20914,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>11.4</v>
+        <v>15.7</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20916,13 +20922,13 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J175" t="n">
-        <v>5.5</v>
+        <v>5.77</v>
       </c>
       <c r="K175" t="n">
-        <v>5.5</v>
+        <v>5.73</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -20937,12 +20943,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Lahdo</t>
+          <t>Fofana Sa.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20960,7 +20966,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20968,13 +20974,13 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -20989,35 +20995,51 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Camara A.</t>
+          <t>Lahdo</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
+      <c r="G177" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
@@ -21025,22 +21047,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Dagasso</t>
+          <t>Camara A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
@@ -21061,12 +21083,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Forson O.</t>
+          <t>Dagasso</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -21094,8 +21116,44 @@
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Forson O.</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P179"/>
+  <autoFilter ref="A1:P180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4155,7 +4155,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E;W</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Dd;E</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Dd;E</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Dd;E</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Dd;E</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;Dc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T;A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T;A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T;A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T;A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;W</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15568,7 +15568,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15609,7 +15609,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -16505,7 +16505,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -17588,7 +17588,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -18037,7 +18037,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;W</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -18803,7 +18803,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -18860,7 +18860,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;W</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -19601,7 +19601,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;M</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -20057,7 +20057,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -20114,7 +20114,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -20629,7 +20629,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -20711,7 +20711,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -21071,7 +21071,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;W</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -21413,7 +21413,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -21812,7 +21812,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -22211,7 +22211,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -22268,7 +22268,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -22325,7 +22325,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -22439,7 +22439,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -22496,7 +22496,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -22619,7 +22619,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;W</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;C</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -23036,7 +23036,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -23207,7 +23207,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -23565,7 +23565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23777,7 +23777,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24005,7 +24005,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -24119,7 +24119,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24290,7 +24290,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -24901,7 +24901,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -25129,7 +25129,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25357,7 +25357,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -25651,7 +25651,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -25790,7 +25790,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -25847,7 +25847,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -25961,7 +25961,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -26189,7 +26189,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>T;A</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -26588,7 +26588,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -26702,7 +26702,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -26898,7 +26898,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -27062,7 +27062,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -27372,7 +27372,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -27657,7 +27657,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -28147,7 +28147,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$S$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$Q$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$Q$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$Q$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$Q$90</definedName>
   </definedNames>
@@ -4151,7 +4151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q178"/>
+  <dimension ref="A1:Q177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12980,27 +12980,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Matturro</t>
+          <t>Bakoune</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D167" t="n">
         <v>1</v>
       </c>
       <c r="E167" t="n">
+        <v>4</v>
+      </c>
+      <c r="F167" t="n">
         <v>2</v>
-      </c>
-      <c r="F167" t="n">
-        <v>1</v>
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
@@ -13021,24 +13021,24 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Bakoune</t>
+          <t>Abankwah</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D168" t="n">
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F168" t="n">
         <v>2</v>
@@ -13062,40 +13062,56 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Abankwah</t>
+          <t>Ziolkowski</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D169" t="n">
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F169" t="n">
-        <v>2</v>
-      </c>
-      <c r="G169" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>9</v>
+      </c>
+      <c r="K169" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="L169" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
@@ -13103,7 +13119,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ziolkowski</t>
+          <t>Goldaniga</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13113,17 +13129,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D170" t="n">
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
@@ -13131,21 +13147,21 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>23.6</v>
+        <v>12.6</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>5.94</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -13160,27 +13176,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Goldaniga</t>
+          <t>Missori</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
@@ -13217,12 +13233,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Missori</t>
+          <t>Pieragnolo</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -13234,10 +13250,10 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
@@ -13274,17 +13290,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Pieragnolo</t>
+          <t>Amey</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -13301,29 +13317,13 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H173" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" t="n">
-        <v>0</v>
-      </c>
-      <c r="N173" t="n">
-        <v>0</v>
-      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
@@ -13331,27 +13331,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Amey</t>
+          <t>Matturro</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D174" t="n">
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Gelli J.</t>
+          <t>Antov</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13382,17 +13382,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D175" t="n">
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
@@ -13413,27 +13413,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Antov</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D176" t="n">
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
@@ -13454,17 +13454,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Omar Fayed</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -13492,49 +13492,8 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Omar Fayed</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Dc</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" t="n">
-        <v>1</v>
-      </c>
-      <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q178"/>
+  <autoFilter ref="A1:Q177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$184</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$184</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1030,10 +1030,10 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1892,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2758,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3433,10 +3433,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -6346,13 +6346,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -6840,10 +6840,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -7188,10 +7188,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7275,10 +7275,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7708,10 +7708,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -7795,10 +7795,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -8670,10 +8670,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -9014,10 +9014,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -9449,10 +9449,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -9710,10 +9710,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -9797,10 +9797,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -9884,13 +9884,13 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -10578,10 +10578,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -10752,10 +10752,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -11448,10 +11448,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -11794,10 +11794,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -12138,10 +12138,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -13122,10 +13122,10 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -13381,10 +13381,10 @@
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -13727,10 +13727,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -14591,10 +14591,10 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -15190,10 +15190,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -15623,10 +15623,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -15710,16 +15710,16 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" t="n">
         <v>9</v>
@@ -15882,10 +15882,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -15967,10 +15967,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -16137,10 +16137,10 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -16520,10 +16520,10 @@
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -16642,10 +16642,10 @@
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -16947,10 +16947,10 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -17008,10 +17008,10 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -18427,10 +18427,10 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -18686,10 +18686,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -18771,10 +18771,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -19200,10 +19200,10 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T162" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -19287,10 +19287,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T163" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -19792,10 +19792,10 @@
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T170" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U170" t="n">
         <v>0</v>
@@ -21256,10 +21256,10 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -22272,16 +22272,16 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
         <v>3</v>
@@ -22359,10 +22359,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -22444,16 +22444,16 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
@@ -22618,10 +22618,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -22705,10 +22705,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -25373,10 +25373,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -26154,10 +26154,10 @@
         <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -26241,10 +26241,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -26415,10 +26415,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -26502,10 +26502,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -26587,16 +26587,16 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" t="n">
         <v>2</v>
@@ -26674,10 +26674,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -26933,10 +26933,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -27107,10 +27107,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -27194,10 +27194,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -27538,10 +27538,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -27690,10 +27690,10 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -27751,10 +27751,10 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -28648,10 +28648,10 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -28822,16 +28822,16 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" t="n">
         <v>4</v>
@@ -29686,10 +29686,10 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -29858,10 +29858,10 @@
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -30119,16 +30119,16 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" t="n">
         <v>4</v>
@@ -30291,10 +30291,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -30550,10 +30550,10 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -30811,10 +30811,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -31495,10 +31495,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -31665,10 +31665,10 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -31730,10 +31730,10 @@
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -31791,10 +31791,10 @@
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -31913,13 +31913,13 @@
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -32035,10 +32035,10 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -32157,10 +32157,10 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -32340,10 +32340,10 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -32597,10 +32597,10 @@
         <v>1</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -33467,10 +33467,10 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -33641,10 +33641,10 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -33987,10 +33987,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -34335,10 +34335,10 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T161" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U161" t="n">
         <v>0</v>
@@ -34762,10 +34762,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T166" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -34847,13 +34847,13 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T167" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -35019,10 +35019,10 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -36010,10 +36010,10 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T182" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U182" t="n">
         <v>0</v>
@@ -36161,7 +36161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA89"/>
+  <dimension ref="A1:AA88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -36361,7 +36361,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -36568,10 +36568,10 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -36766,7 +36766,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>86.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -36888,10 +36888,10 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -36940,7 +36940,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Douvikas</t>
+          <t>Esposito F.P.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -37183,17 +37183,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -37209,46 +37209,44 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K12" t="n">
-        <v>6.18</v>
+        <v>6.26</v>
       </c>
       <c r="L12" t="n">
-        <v>7.38</v>
+        <v>7.02</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.63</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>0.632</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -37260,7 +37258,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Esposito F.P.</t>
+          <t>Douvikas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -37270,17 +37268,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -37288,7 +37286,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -37296,44 +37294,46 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K13" t="n">
-        <v>6.26</v>
+        <v>6.18</v>
       </c>
       <c r="L13" t="n">
-        <v>7.02</v>
+        <v>7.38</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.63</v>
+      </c>
       <c r="O13" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -37373,7 +37373,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -37580,10 +37580,10 @@
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -37632,7 +37632,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>71.7</v>
+        <v>71.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -37806,11 +37806,11 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>62.2</v>
+        <v>61.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>60.6</v>
+        <v>60.1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>78</v>
+        <v>77.7</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>77.3</v>
+        <v>77</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>74.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>74.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>72.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>64.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>61.2</v>
+        <v>60.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>61</v>
+        <v>60.7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -38711,10 +38711,10 @@
         <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -38735,27 +38735,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Santos A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E30" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>56.7</v>
+        <v>56.1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -38771,36 +38771,36 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>5.77</v>
+        <v>6.35</v>
       </c>
       <c r="L30" t="n">
-        <v>6.33</v>
+        <v>7.23</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>0.789</v>
+        <v>0.342</v>
       </c>
       <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>6</v>
       </c>
-      <c r="Q30" t="n">
-        <v>2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
@@ -38808,7 +38808,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -38820,27 +38820,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Santos A.</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>56.4</v>
+        <v>56.1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -38856,29 +38856,29 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K31" t="n">
-        <v>6.35</v>
+        <v>5.77</v>
       </c>
       <c r="L31" t="n">
-        <v>7.23</v>
+        <v>6.33</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>0.342</v>
+        <v>0.789</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -38893,7 +38893,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -38933,7 +38933,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>53.7</v>
+        <v>53</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>47.4</v>
+        <v>47</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>44.6</v>
+        <v>44.3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -39401,10 +39401,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -39425,27 +39425,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Yeboah J.</t>
+          <t>Ghedjemis</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>34</v>
+        <v>14.4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -39461,26 +39461,26 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>5.91</v>
+        <v>6.2</v>
       </c>
       <c r="L38" t="n">
-        <v>5.98</v>
+        <v>6.1</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>0.737</v>
+        <v>0.132</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -39498,7 +39498,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -39510,56 +39510,56 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ghedjemis</t>
+          <t>Ratkov</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="n">
+        <v>32</v>
+      </c>
+      <c r="F39" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>9</v>
       </c>
-      <c r="E39" t="n">
-        <v>30</v>
-      </c>
-      <c r="F39" t="n">
-        <v>15</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>14.3</v>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>Trappola</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>6.2</v>
+        <v>5.64</v>
       </c>
       <c r="L39" t="n">
-        <v>6.1</v>
+        <v>5.64</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>0.132</v>
+        <v>0.184</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -39583,7 +39583,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -39595,7 +39595,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ratkov</t>
+          <t>Kevin Carlos</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -39605,56 +39605,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E40" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F40" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>9</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>7</v>
-      </c>
-      <c r="K40" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="L40" t="n">
-        <v>5.64</v>
-      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
         <v>0</v>
       </c>
@@ -39667,12 +39647,8 @@
       <c r="V40" t="n">
         <v>0</v>
       </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -39680,7 +39656,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kevin Carlos</t>
+          <t>Adams A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -39690,17 +39666,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -39721,10 +39697,10 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -39741,7 +39717,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Adams A.</t>
+          <t>Romero D.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -39751,17 +39727,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F42" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
@@ -39802,46 +39778,66 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Romero D.</t>
+          <t>Nkunku</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E43" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F43" t="n">
-        <v>19</v>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>26</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6.87</v>
+      </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="P43" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>5</v>
+      </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
@@ -39854,8 +39850,12 @@
       <c r="V43" t="n">
         <v>0</v>
       </c>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
@@ -39863,27 +39863,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nkunku</t>
+          <t>Bonny</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>74.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -39899,35 +39899,37 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K44" t="n">
-        <v>5.94</v>
+        <v>6.15</v>
       </c>
       <c r="L44" t="n">
-        <v>6.87</v>
+        <v>6.83</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.32</v>
+      </c>
       <c r="O44" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.842</v>
       </c>
       <c r="P44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -39936,7 +39938,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -39948,27 +39950,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bonny</t>
+          <t>Boga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -39976,36 +39978,34 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>67.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>6.15</v>
+        <v>6.19</v>
       </c>
       <c r="L45" t="n">
-        <v>6.83</v>
+        <v>7.15</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.32</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>0.842</v>
+        <v>0.342</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -40035,27 +40035,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Boga</t>
+          <t>Zapata D.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -40063,37 +40063,39 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>60.3</v>
+        <v>55.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>6.19</v>
+        <v>5.83</v>
       </c>
       <c r="L46" t="n">
-        <v>7.15</v>
+        <v>6.13</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="O46" t="n">
-        <v>0.342</v>
+        <v>0.588</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -40108,7 +40110,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -40120,27 +40122,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Zapata D.</t>
+          <t>Giovane</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
@@ -40148,7 +40150,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>56.4</v>
+        <v>55.7</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -40156,31 +40158,29 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="L47" t="n">
-        <v>6.13</v>
+        <v>6.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
-      </c>
-      <c r="N47" t="n">
-        <v>-1.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>0.588</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="P47" t="n">
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -40195,7 +40195,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -40207,12 +40207,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Giovane</t>
+          <t>Neres</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -40221,13 +40221,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
@@ -40235,34 +40235,36 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>56</v>
+        <v>55.1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="L48" t="n">
-        <v>6.45</v>
+        <v>6.84</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.12</v>
+      </c>
       <c r="O48" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.539</v>
       </c>
       <c r="P48" t="n">
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -40280,7 +40282,7 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
@@ -40292,27 +40294,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Neres</t>
+          <t>Mota</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -40320,36 +40322,36 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>55.1</v>
+        <v>53.7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K49" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="L49" t="n">
-        <v>6.84</v>
+        <v>6.31</v>
       </c>
       <c r="M49" t="n">
         <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.539</v>
+        <v>0.842</v>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -40379,7 +40381,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mota</t>
+          <t>Noslin</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -40389,17 +40391,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
@@ -40407,7 +40409,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>54.3</v>
+        <v>52.3</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -40415,29 +40417,29 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K50" t="n">
-        <v>5.84</v>
+        <v>6.02</v>
       </c>
       <c r="L50" t="n">
-        <v>6.31</v>
+        <v>6.5</v>
       </c>
       <c r="M50" t="n">
+        <v>3</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="P50" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q50" t="n">
         <v>2</v>
       </c>
-      <c r="N50" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="P50" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -40454,10 +40456,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
@@ -40466,7 +40468,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noslin</t>
+          <t>Vitinha O.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -40476,17 +40478,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
@@ -40494,21 +40496,21 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>52.9</v>
+        <v>50.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K51" t="n">
-        <v>6.02</v>
+        <v>5.95</v>
       </c>
       <c r="L51" t="n">
-        <v>6.5</v>
+        <v>6.39</v>
       </c>
       <c r="M51" t="n">
         <v>3</v>
@@ -40520,19 +40522,19 @@
         <v>0.518</v>
       </c>
       <c r="P51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -40541,10 +40543,10 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
@@ -40553,27 +40555,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vitinha O.</t>
+          <t>Milik</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F52" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -40581,36 +40583,36 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>51.1</v>
+        <v>47.5</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
-        <v>6.39</v>
+        <v>6</v>
       </c>
       <c r="M52" t="n">
         <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.26</v>
+        <v>3.58</v>
       </c>
       <c r="O52" t="n">
-        <v>0.518</v>
+        <v>0.228</v>
       </c>
       <c r="P52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -40628,7 +40630,7 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -40640,7 +40642,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Milik</t>
+          <t>Elphege</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -40650,14 +40652,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F53" t="n">
         <v>6</v>
@@ -40668,7 +40670,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>48.2</v>
+        <v>47.3</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -40676,37 +40678,35 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
         <v>6</v>
       </c>
       <c r="L53" t="n">
-        <v>6</v>
+        <v>6.88</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" t="n">
-        <v>3.58</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
-        <v>0.228</v>
+        <v>0.211</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -40727,56 +40727,58 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Elphege</t>
+          <t>Maldini</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>T;A</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>22</v>
+      </c>
+      <c r="F54" t="n">
+        <v>11</v>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>18</v>
+      </c>
+      <c r="K54" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="M54" t="n">
         <v>3</v>
       </c>
-      <c r="E54" t="n">
-        <v>11</v>
-      </c>
-      <c r="F54" t="n">
-        <v>6</v>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>8</v>
-      </c>
-      <c r="K54" t="n">
-        <v>6</v>
-      </c>
-      <c r="L54" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>-0.42</v>
+      </c>
       <c r="O54" t="n">
-        <v>0.211</v>
+        <v>0.535</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
@@ -40788,10 +40790,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -40800,7 +40802,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
@@ -40812,27 +40814,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Maldini</t>
+          <t>Stulic</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>T;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -40840,7 +40842,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>42.9</v>
+        <v>38.6</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -40848,37 +40850,35 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K55" t="n">
-        <v>5.94</v>
+        <v>5.73</v>
       </c>
       <c r="L55" t="n">
-        <v>6.31</v>
+        <v>6.12</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-0.42</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
-        <v>0.535</v>
+        <v>0.789</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -40899,27 +40899,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Stulic</t>
+          <t>Sulemana K.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>38.8</v>
+        <v>34.7</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -40935,44 +40935,44 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>5.73</v>
+        <v>6</v>
       </c>
       <c r="L56" t="n">
-        <v>6.12</v>
+        <v>6.24</v>
       </c>
       <c r="M56" t="n">
         <v>1</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
-        <v>0.789</v>
+        <v>0.553</v>
       </c>
       <c r="P56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
         <v>4</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
@@ -40984,7 +40984,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sulemana K.</t>
+          <t>Yeboah J.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -40994,17 +40994,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
@@ -41012,43 +41012,43 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>34.8</v>
+        <v>34</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K57" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="L57" t="n">
-        <v>6.24</v>
+        <v>5.98</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>0.553</v>
+        <v>0.737</v>
       </c>
       <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -41057,7 +41057,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -41069,27 +41069,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ekhator</t>
+          <t>Gimenez</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>34.3</v>
+        <v>25.8</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -41105,28 +41105,28 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>5.96</v>
+        <v>5.5</v>
       </c>
       <c r="L58" t="n">
-        <v>6.28</v>
+        <v>5.53</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>0.18</v>
+        <v>-1.22</v>
       </c>
       <c r="O58" t="n">
-        <v>0.526</v>
+        <v>0.355</v>
       </c>
       <c r="P58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -41144,7 +41144,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
@@ -41156,7 +41156,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gimenez</t>
+          <t>Morata</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -41166,17 +41166,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>25.7</v>
+        <v>19.3</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -41192,31 +41192,31 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K59" t="n">
         <v>5.5</v>
       </c>
       <c r="L59" t="n">
-        <v>5.53</v>
+        <v>5.21</v>
       </c>
       <c r="M59" t="n">
         <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>-1.22</v>
+        <v>-1.67</v>
       </c>
       <c r="O59" t="n">
-        <v>0.355</v>
+        <v>0.434</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -41234,7 +41234,7 @@
         <v>2</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
@@ -41243,7 +41243,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Morata</t>
+          <t>Camarda</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -41253,51 +41253,51 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
+        <v>20</v>
+      </c>
+      <c r="F60" t="n">
         <v>10</v>
       </c>
-      <c r="F60" t="n">
-        <v>5</v>
-      </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>19.2</v>
+        <v>15.5</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K60" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L60" t="n">
-        <v>5.21</v>
+        <v>5.64</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
-        <v>-1.67</v>
+        <v>1.94</v>
       </c>
       <c r="O60" t="n">
-        <v>0.434</v>
+        <v>0.211</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -41318,10 +41318,10 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
@@ -41330,7 +41330,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Camarda</t>
+          <t>Mutandwa</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -41340,57 +41340,55 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D61" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" t="n">
+        <v>15</v>
+      </c>
+      <c r="F61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
         <v>5</v>
       </c>
-      <c r="E61" t="n">
-        <v>20</v>
-      </c>
-      <c r="F61" t="n">
-        <v>10</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>18</v>
-      </c>
       <c r="K61" t="n">
-        <v>5.67</v>
+        <v>5.9</v>
       </c>
       <c r="L61" t="n">
-        <v>5.64</v>
+        <v>5.9</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1.94</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
-        <v>0.211</v>
+        <v>0.132</v>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -41405,7 +41403,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -41417,21 +41415,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mutandwa</t>
+          <t>Kvernadze</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
         <v>15</v>
@@ -41445,7 +41443,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -41453,20 +41451,20 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="L62" t="n">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="M62" t="n">
         <v>1</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>0.132</v>
+        <v>0.053</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -41478,10 +41476,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -41502,12 +41500,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kvernadze</t>
+          <t>Raimondo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -41516,13 +41514,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
@@ -41530,7 +41528,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -41538,20 +41536,22 @@
         </is>
       </c>
       <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M63" t="n">
         <v>2</v>
       </c>
-      <c r="K63" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L63" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>6</v>
+      </c>
       <c r="O63" t="n">
-        <v>0.053</v>
+        <v>0.013</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -41563,10 +41563,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -41587,27 +41587,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Raimondo</t>
+          <t>Frigan</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -41623,22 +41623,20 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
-      </c>
-      <c r="N64" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -41674,71 +41672,51 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Frigan</t>
+          <t>Geubbels</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
-      <c r="H65" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -41746,12 +41724,8 @@
       <c r="V65" t="n">
         <v>0</v>
       </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
@@ -41759,7 +41733,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Geubbels</t>
+          <t>Rrahmani Al.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -41769,17 +41743,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
@@ -41820,7 +41794,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Rrahmani Al.</t>
+          <t>Adorante</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -41834,13 +41808,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
@@ -41881,27 +41855,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Adorante</t>
+          <t>Robinson J.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" t="n">
         <v>5</v>
-      </c>
-      <c r="E68" t="n">
-        <v>14</v>
-      </c>
-      <c r="F68" t="n">
-        <v>7</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
@@ -41942,51 +41916,73 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Robinson J.</t>
+          <t>Borrelli</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>26</v>
+      </c>
+      <c r="K69" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="L69" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="P69" t="n">
         <v>5</v>
       </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -41994,8 +41990,12 @@
       <c r="V69" t="n">
         <v>0</v>
       </c>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
+      <c r="W69" t="n">
+        <v>4</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
@@ -42003,7 +42003,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Borrelli</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -42013,63 +42013,63 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
         <v>9</v>
       </c>
-      <c r="F70" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>26</v>
-      </c>
       <c r="K70" t="n">
-        <v>5.92</v>
+        <v>5.72</v>
       </c>
       <c r="L70" t="n">
-        <v>6.46</v>
+        <v>6</v>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>0.46</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O70" t="n">
-        <v>0.355</v>
+        <v>0.667</v>
       </c>
       <c r="P70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -42078,7 +42078,7 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X70" t="n">
         <v>0</v>
@@ -42090,7 +42090,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Mendy P.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -42100,17 +42100,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>45.1</v>
+        <v>35.8</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -42126,25 +42126,23 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K71" t="n">
-        <v>5.72</v>
+        <v>5.94</v>
       </c>
       <c r="L71" t="n">
-        <v>6</v>
+        <v>6.62</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
-      </c>
-      <c r="N71" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
-        <v>0.667</v>
+        <v>0.211</v>
       </c>
       <c r="P71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -42153,10 +42151,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -42177,27 +42175,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mendy P.</t>
+          <t>Ekhator</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
@@ -42205,7 +42203,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>36</v>
+        <v>34.3</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -42213,23 +42211,25 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K72" t="n">
-        <v>5.94</v>
+        <v>5.96</v>
       </c>
       <c r="L72" t="n">
-        <v>6.62</v>
+        <v>6.28</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.18</v>
+      </c>
       <c r="O72" t="n">
-        <v>0.211</v>
+        <v>0.526</v>
       </c>
       <c r="P72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -42250,7 +42250,7 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X72" t="n">
         <v>0</v>
@@ -42290,7 +42290,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -42323,10 +42323,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -42347,24 +42347,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Buksa</t>
+          <t>Kuhn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -42375,7 +42375,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>33.2</v>
+        <v>29.2</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -42383,26 +42383,26 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K74" t="n">
-        <v>5.88</v>
+        <v>5.96</v>
       </c>
       <c r="L74" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
-        <v>0.553</v>
+        <v>0.368</v>
       </c>
       <c r="P74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -42420,7 +42420,7 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -42432,24 +42432,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kuhn</t>
+          <t>Vaz</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -42460,7 +42460,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>29.5</v>
+        <v>25</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -42468,26 +42468,26 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K75" t="n">
-        <v>5.96</v>
+        <v>5.93</v>
       </c>
       <c r="L75" t="n">
-        <v>6.25</v>
+        <v>6.36</v>
       </c>
       <c r="M75" t="n">
         <v>1</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
-        <v>0.368</v>
+        <v>0.184</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -42517,59 +42517,61 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Vaz</t>
+          <t>N'Dri</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
+        <v>9</v>
+      </c>
+      <c r="F76" t="n">
         <v>4</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>17</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="L76" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="M76" t="n">
         <v>2</v>
       </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>7</v>
-      </c>
-      <c r="K76" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="L76" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>0.23</v>
+      </c>
       <c r="O76" t="n">
-        <v>0.184</v>
+        <v>0.316</v>
       </c>
       <c r="P76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -42578,10 +42580,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -42590,7 +42592,7 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X76" t="n">
         <v>0</v>
@@ -42602,24 +42604,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>N'Dri</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
         <v>4</v>
@@ -42630,7 +42632,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>22.6</v>
+        <v>19.1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -42638,46 +42640,44 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K77" t="n">
-        <v>5.82</v>
+        <v>5.77</v>
       </c>
       <c r="L77" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
         <v>2</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="P77" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>3</v>
       </c>
       <c r="X77" t="n">
         <v>0</v>
@@ -42689,7 +42689,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Bayo V.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -42703,13 +42703,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -42725,26 +42725,26 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K78" t="n">
-        <v>5.77</v>
+        <v>5.75</v>
       </c>
       <c r="L78" t="n">
-        <v>5.92</v>
+        <v>5.83</v>
       </c>
       <c r="M78" t="n">
         <v>1</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
-        <v>0.342</v>
+        <v>0.316</v>
       </c>
       <c r="P78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -42753,7 +42753,7 @@
         <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -42762,7 +42762,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X78" t="n">
         <v>0</v>
@@ -42774,7 +42774,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Bayo V.</t>
+          <t>Kulenovic</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -42784,17 +42784,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>17.8</v>
+        <v>16.3</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -42810,20 +42810,20 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K79" t="n">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="L79" t="n">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="M79" t="n">
         <v>1</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
-        <v>0.316</v>
+        <v>0.184</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -42835,10 +42835,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -42847,7 +42847,7 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X79" t="n">
         <v>0</v>
@@ -42859,27 +42859,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kulenovic</t>
+          <t>Albarracin</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>16.3</v>
+        <v>13.2</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -42895,26 +42895,26 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="L80" t="n">
-        <v>5.79</v>
+        <v>6</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
-        <v>0.184</v>
+        <v>0.053</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -42932,7 +42932,7 @@
         <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
         <v>0</v>
@@ -42944,12 +42944,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Albarracin</t>
+          <t>Trepy</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -42961,7 +42961,7 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>13.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -42980,20 +42980,20 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="L81" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="M81" t="n">
         <v>1</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
-        <v>0.053</v>
+        <v>0.079</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -43029,7 +43029,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Trepy</t>
+          <t>Havel</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -43039,56 +43039,36 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H82" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>3</v>
-      </c>
-      <c r="K82" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="L82" t="n">
-        <v>5.67</v>
-      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
         <v>0</v>
       </c>
@@ -43101,12 +43081,8 @@
       <c r="V82" t="n">
         <v>0</v>
       </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
@@ -43114,7 +43090,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Havel</t>
+          <t>Varela G.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -43124,14 +43100,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F83" t="n">
         <v>4</v>
@@ -43155,13 +43131,13 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -43175,27 +43151,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Varela G.</t>
+          <t>Lontani</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
         <v>3</v>
       </c>
-      <c r="E84" t="n">
-        <v>7</v>
-      </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
@@ -43219,10 +43195,10 @@
         <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -43236,46 +43212,68 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lontani</t>
+          <t>Azon</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
         <v>2</v>
       </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
       <c r="S85" t="n">
         <v>0</v>
       </c>
@@ -43288,8 +43286,12 @@
       <c r="V85" t="n">
         <v>0</v>
       </c>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
@@ -43297,17 +43299,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azon</t>
+          <t>Lisman</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -43324,41 +43326,19 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H86" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>2</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
         <v>0</v>
       </c>
@@ -43371,12 +43351,8 @@
       <c r="V86" t="n">
         <v>0</v>
       </c>
-      <c r="W86" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" t="n">
-        <v>0</v>
-      </c>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr"/>
@@ -43384,12 +43360,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lisman</t>
+          <t>Lauberbach</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -43445,7 +43421,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Lauberbach</t>
+          <t>De Martis</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -43455,7 +43431,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -43503,69 +43479,8 @@
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>De Martis</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Pc</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AA89"/>
+  <autoFilter ref="A1:AA88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$184</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$184</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -6087,10 +6087,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -6172,10 +6172,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -7536,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -7708,10 +7708,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -8400,10 +8400,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -9623,10 +9623,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -12197,10 +12197,10 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -13723,10 +13723,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -13810,10 +13810,10 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -21752,10 +21752,10 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -22962,10 +22962,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -23308,10 +23308,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -23865,10 +23865,10 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -24157,10 +24157,10 @@
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -25282,10 +25282,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -26063,10 +26063,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -27018,10 +27018,10 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -27636,10 +27636,10 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -28250,10 +28250,10 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -28337,13 +28337,13 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -36161,7 +36161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA87"/>
+  <dimension ref="A1:AA88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -36653,13 +36653,13 @@
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -37408,10 +37408,10 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -37667,16 +37667,16 @@
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -37778,7 +37778,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Simeone</t>
+          <t>Castro S.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -37788,17 +37788,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -37806,36 +37806,36 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>6.08</v>
+        <v>5.93</v>
       </c>
       <c r="L19" t="n">
-        <v>7.09</v>
+        <v>6.51</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.09</v>
+        <v>-0.15</v>
       </c>
       <c r="O19" t="n">
-        <v>0.596</v>
+        <v>0.64</v>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -37844,7 +37844,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -37853,7 +37853,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -37865,73 +37865,73 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Leao</t>
+          <t>Simeone</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>38</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
+        <v>40</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>1a Fascia</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>84.5</v>
+        <v>59.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K20" t="n">
-        <v>5.88</v>
+        <v>6.08</v>
       </c>
       <c r="L20" t="n">
-        <v>6.86</v>
+        <v>7.09</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.33</v>
+        <v>1.09</v>
       </c>
       <c r="O20" t="n">
-        <v>0.833</v>
+        <v>0.596</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -37940,7 +37940,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -37952,7 +37952,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Esposito Se.</t>
+          <t>Leao</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -37962,17 +37962,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -37980,39 +37980,39 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>77.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
-        <v>6.26</v>
+        <v>5.88</v>
       </c>
       <c r="L21" t="n">
-        <v>6.88</v>
+        <v>6.86</v>
       </c>
       <c r="M21" t="n">
         <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.64</v>
+        <v>-0.33</v>
       </c>
       <c r="O21" t="n">
-        <v>0.605</v>
+        <v>0.833</v>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -38027,7 +38027,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -38039,7 +38039,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Soulè</t>
+          <t>Esposito Se.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -38049,17 +38049,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -38067,54 +38067,54 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>76.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K22" t="n">
-        <v>6.12</v>
+        <v>6.26</v>
       </c>
       <c r="L22" t="n">
-        <v>6.83</v>
+        <v>6.88</v>
       </c>
       <c r="M22" t="n">
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.22</v>
+        <v>2.64</v>
       </c>
       <c r="O22" t="n">
-        <v>0.798</v>
+        <v>0.605</v>
       </c>
       <c r="P22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>6</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -38126,27 +38126,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pinamonti</t>
+          <t>Soulè</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>74.2</v>
+        <v>76.7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -38162,37 +38162,37 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>5.88</v>
+        <v>6.12</v>
       </c>
       <c r="L23" t="n">
-        <v>6.62</v>
+        <v>6.83</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -38201,10 +38201,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
@@ -38213,85 +38213,85 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Adams C.</t>
+          <t>Pinamonti</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" t="n">
+        <v>51</v>
+      </c>
+      <c r="F24" t="n">
+        <v>26</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>34</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="P24" t="n">
         <v>9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>33</v>
-      </c>
-      <c r="F24" t="n">
-        <v>16</v>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>32</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="P24" t="n">
-        <v>6</v>
       </c>
       <c r="Q24" t="n">
         <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
@@ -38300,65 +38300,65 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dovbyk</t>
+          <t>Adams C.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>33</v>
+      </c>
+      <c r="F25" t="n">
         <v>16</v>
       </c>
-      <c r="E25" t="n">
-        <v>58</v>
-      </c>
-      <c r="F25" t="n">
-        <v>29</v>
-      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>63.6</v>
+        <v>71.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>5.98</v>
       </c>
       <c r="L25" t="n">
-        <v>6.77</v>
+        <v>6.64</v>
       </c>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.42</v>
+        <v>-0.12</v>
       </c>
       <c r="O25" t="n">
-        <v>0.592</v>
+        <v>0.882</v>
       </c>
       <c r="P25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -38366,10 +38366,10 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -38387,7 +38387,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Castro S.</t>
+          <t>Dovbyk</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -38397,17 +38397,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>61.1</v>
+        <v>63.6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -38423,26 +38423,26 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>6.51</v>
+        <v>6.77</v>
       </c>
       <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="P26" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P26" t="n">
-        <v>7</v>
-      </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
@@ -38450,10 +38450,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -38462,7 +38462,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -38537,10 +38537,10 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -39338,27 +39338,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yeboah J.</t>
+          <t>Tourè E.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -39374,26 +39374,28 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-2.46</v>
+      </c>
       <c r="O37" t="n">
-        <v>0.737</v>
+        <v>0.079</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -39402,7 +39404,7 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -39411,7 +39413,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -39423,27 +39425,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tourè E.</t>
+          <t>Ghedjemis</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F38" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
@@ -39451,7 +39453,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>33.2</v>
+        <v>13.6</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -39459,22 +39461,20 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-2.46</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>0.079</v>
+        <v>0.132</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -39486,10 +39486,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -39498,7 +39498,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -39510,66 +39510,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ghedjemis</t>
+          <t>Kevin Carlos</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>5</v>
-      </c>
-      <c r="K39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>6.1</v>
-      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
         <v>0</v>
       </c>
@@ -39582,12 +39562,8 @@
       <c r="V39" t="n">
         <v>0</v>
       </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -39595,7 +39571,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kevin Carlos</t>
+          <t>Adams A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -39605,17 +39581,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F40" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
@@ -39636,10 +39612,10 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -39656,7 +39632,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Adams A.</t>
+          <t>Romero D.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -39666,17 +39642,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F41" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -39697,10 +39673,10 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -39717,7 +39693,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Romero D.</t>
+          <t>Osmajic</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -39727,17 +39703,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
@@ -40984,7 +40960,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lang</t>
+          <t>Yeboah J.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -40994,17 +40970,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
@@ -41012,28 +40988,28 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>32.2</v>
+        <v>33.6</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K57" t="n">
-        <v>6.04</v>
+        <v>5.91</v>
       </c>
       <c r="L57" t="n">
-        <v>6.32</v>
+        <v>5.98</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>0.368</v>
+        <v>0.737</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
@@ -41057,7 +41033,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -41069,35 +41045,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gimenez</t>
+          <t>Lang</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>12</v>
+      </c>
+      <c r="F58" t="n">
         <v>6</v>
       </c>
-      <c r="E58" t="n">
-        <v>10</v>
-      </c>
-      <c r="F58" t="n">
-        <v>5</v>
-      </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>25.3</v>
+        <v>32.2</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -41105,37 +41081,35 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>5.5</v>
+        <v>6.04</v>
       </c>
       <c r="L58" t="n">
-        <v>5.53</v>
+        <v>6.32</v>
       </c>
       <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
         <v>2</v>
       </c>
-      <c r="N58" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -41156,82 +41130,82 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>N'Dri</t>
+          <t>Gimenez</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
         <v>15</v>
       </c>
-      <c r="F59" t="n">
-        <v>8</v>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>17</v>
-      </c>
       <c r="K59" t="n">
-        <v>5.82</v>
+        <v>5.5</v>
       </c>
       <c r="L59" t="n">
-        <v>6.09</v>
+        <v>5.53</v>
       </c>
       <c r="M59" t="n">
         <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>0.23</v>
+        <v>-1.22</v>
       </c>
       <c r="O59" t="n">
-        <v>0.316</v>
+        <v>0.355</v>
       </c>
       <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
         <v>2</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>1</v>
-      </c>
-      <c r="T59" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>3</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -41243,27 +41217,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Camarda</t>
+          <t>N'Dri</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
@@ -41271,54 +41245,54 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>15</v>
+        <v>21.9</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K60" t="n">
-        <v>5.67</v>
+        <v>5.82</v>
       </c>
       <c r="L60" t="n">
-        <v>5.64</v>
+        <v>6.09</v>
       </c>
       <c r="M60" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
         <v>3</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="P60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -41330,7 +41304,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mutandwa</t>
+          <t>Camarda</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -41340,55 +41314,57 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" t="n">
         <v>10</v>
       </c>
-      <c r="F61" t="n">
-        <v>5</v>
-      </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K61" t="n">
-        <v>5.9</v>
+        <v>5.67</v>
       </c>
       <c r="L61" t="n">
-        <v>5.9</v>
+        <v>5.64</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.94</v>
+      </c>
       <c r="O61" t="n">
-        <v>0.132</v>
+        <v>0.211</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -41403,7 +41379,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -41415,27 +41391,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kvernadze</t>
+          <t>Mutandwa</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
@@ -41443,28 +41419,28 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="L62" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="M62" t="n">
         <v>1</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>0.053</v>
+        <v>0.132</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -41476,10 +41452,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -41500,27 +41476,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ratkov</t>
+          <t>Kvernadze</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
@@ -41528,7 +41504,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -41536,20 +41512,20 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="L63" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="M63" t="n">
         <v>1</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
-        <v>0.184</v>
+        <v>0.053</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -41561,10 +41537,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -41585,7 +41561,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Raimondo</t>
+          <t>Ratkov</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -41595,48 +41571,46 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="n">
+        <v>26</v>
+      </c>
+      <c r="F64" t="n">
+        <v>13</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
         <v>7</v>
       </c>
-      <c r="E64" t="n">
-        <v>22</v>
-      </c>
-      <c r="F64" t="n">
-        <v>11</v>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>5.64</v>
       </c>
       <c r="L64" t="n">
-        <v>6</v>
+        <v>5.64</v>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
-      </c>
-      <c r="N64" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>0.013</v>
+        <v>0.184</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -41648,10 +41622,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -41672,27 +41646,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Frigan</t>
+          <t>Raimondo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
@@ -41700,28 +41674,30 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>6</v>
+      </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -41733,10 +41709,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -42883,46 +42859,66 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Havel</t>
+          <t>Frigan</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
       <c r="S80" t="n">
         <v>0</v>
       </c>
@@ -42935,8 +42931,12 @@
       <c r="V80" t="n">
         <v>0</v>
       </c>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
@@ -42944,27 +42944,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Robinson J.</t>
+          <t>Havel</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
@@ -43005,12 +43005,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Varela G.</t>
+          <t>Robinson J.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -43019,13 +43019,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
@@ -43046,13 +43046,13 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -43066,27 +43066,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Lontani</t>
+          <t>Varela G.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
@@ -43110,10 +43110,10 @@
         <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -43127,73 +43127,51 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azon</t>
+          <t>Lontani</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>2</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -43201,12 +43179,8 @@
       <c r="V84" t="n">
         <v>0</v>
       </c>
-      <c r="W84" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0</v>
-      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
@@ -43214,17 +43188,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lisman</t>
+          <t>Azon</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -43241,19 +43215,41 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
       <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
       <c r="S85" t="n">
         <v>0</v>
       </c>
@@ -43266,8 +43262,12 @@
       <c r="V85" t="n">
         <v>0</v>
       </c>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
@@ -43275,12 +43275,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Lauberbach</t>
+          <t>Lisman</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -43336,7 +43336,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>De Martis</t>
+          <t>Lauberbach</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -43346,7 +43346,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -43394,8 +43394,69 @@
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>De Martis</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pc</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA87"/>
+  <autoFilter ref="A1:AA88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>40</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>30</v>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>32</v>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>28</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
         <v>12</v>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
         <v>253</v>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
         <v>60</v>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>37</v>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>27</v>
@@ -9647,27 +9647,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Celik</t>
+          <t>Tiago Gabriel</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B;Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
@@ -9683,28 +9683,28 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K46" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
-        <v>6.27</v>
+        <v>6.01</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>0.46</v>
+        <v>-0.24</v>
       </c>
       <c r="O46" t="n">
-        <v>0.649</v>
+        <v>0.5</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -9713,19 +9713,19 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
@@ -9734,27 +9734,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tiago Gabriel</t>
+          <t>Celik</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>B;Dd;E</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
@@ -9770,49 +9770,49 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K47" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="L47" t="n">
-        <v>6.01</v>
+        <v>6.27</v>
       </c>
       <c r="M47" t="n">
+        <v>3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
         <v>2</v>
       </c>
-      <c r="N47" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P47" t="n">
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>10</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>7</v>
-      </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gallo</t>
+          <t>Kamara H.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10525,14 +10525,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>6</v>
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>58.1</v>
+        <v>59.8</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -10551,28 +10551,28 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K56" t="n">
-        <v>5.95</v>
+        <v>5.88</v>
       </c>
       <c r="L56" t="n">
-        <v>5.99</v>
+        <v>5.87</v>
       </c>
       <c r="M56" t="n">
         <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="O56" t="n">
-        <v>0.895</v>
+        <v>0.763</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -10581,16 +10581,16 @@
         <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
@@ -10602,27 +10602,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pavard</t>
+          <t>Gallo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>6</v>
       </c>
       <c r="E57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -10638,37 +10638,37 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="L57" t="n">
-        <v>6.5</v>
+        <v>5.99</v>
       </c>
       <c r="M57" t="n">
         <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="O57" t="n">
-        <v>0.386</v>
+        <v>0.895</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -10677,7 +10677,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -10689,27 +10689,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tavares N.</t>
+          <t>Pavard</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>54.2</v>
+        <v>54.8</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10725,22 +10725,22 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>5.91</v>
+        <v>6.5</v>
       </c>
       <c r="L58" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.7</v>
+        <v>0.41</v>
       </c>
       <c r="O58" t="n">
-        <v>0.592</v>
+        <v>0.386</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
@@ -11573,7 +11573,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
         <v>13</v>
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
         <v>14</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
         <v>14</v>
@@ -12156,7 +12156,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Koulierakis</t>
+          <t>Doekhi</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12166,14 +12166,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F75" t="n">
         <v>8</v>
@@ -12200,7 +12200,7 @@
         <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -12217,24 +12217,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kaiki</t>
+          <t>Koulierakis</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F76" t="n">
         <v>8</v>
@@ -12258,10 +12258,10 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -12278,17 +12278,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Doekhi</t>
+          <t>Kaiki</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -12319,10 +12319,10 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -13314,21 +13314,21 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kamara H.</t>
+          <t>De Winter</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
         <v>12</v>
@@ -13342,7 +13342,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>59.8</v>
+        <v>59.4</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -13350,28 +13350,28 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K91" t="n">
-        <v>5.88</v>
+        <v>5.75</v>
       </c>
       <c r="L91" t="n">
-        <v>5.87</v>
+        <v>5.9</v>
       </c>
       <c r="M91" t="n">
         <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="O91" t="n">
-        <v>0.763</v>
+        <v>0.675</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -13380,16 +13380,16 @@
         <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X91" t="n">
         <v>0</v>
@@ -13401,21 +13401,21 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>De Winter</t>
+          <t>Kelly L.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
         <v>12</v>
@@ -13429,7 +13429,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>59.4</v>
+        <v>58.6</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -13437,22 +13437,22 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K92" t="n">
-        <v>5.75</v>
+        <v>6.01</v>
       </c>
       <c r="L92" t="n">
-        <v>5.9</v>
+        <v>6.07</v>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.06</v>
+        <v>0.45</v>
       </c>
       <c r="O92" t="n">
-        <v>0.675</v>
+        <v>0.618</v>
       </c>
       <c r="P92" t="n">
         <v>1</v>
@@ -13467,7 +13467,7 @@
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -13476,7 +13476,7 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X92" t="n">
         <v>0</v>
@@ -13488,82 +13488,82 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kelly L.</t>
+          <t>Parisi</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D93" t="n">
         <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
+        <v>5</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>23</v>
+      </c>
+      <c r="K93" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="L93" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3</v>
+      </c>
+      <c r="N93" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
         <v>6</v>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>35</v>
-      </c>
-      <c r="K93" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="L93" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="M93" t="n">
-        <v>2</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="P93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>1</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>1</v>
-      </c>
-      <c r="T93" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
-        <v>4</v>
       </c>
       <c r="X93" t="n">
         <v>0</v>
@@ -13575,12 +13575,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Parisi</t>
+          <t>Joao Mario</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -13589,60 +13589,58 @@
         </is>
       </c>
       <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>12</v>
+      </c>
+      <c r="F94" t="n">
+        <v>6</v>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>14</v>
+      </c>
+      <c r="K94" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="L94" t="n">
+        <v>6</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
         <v>5</v>
       </c>
-      <c r="E94" t="n">
-        <v>10</v>
-      </c>
-      <c r="F94" t="n">
-        <v>5</v>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H94" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>23</v>
-      </c>
-      <c r="K94" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="L94" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="M94" t="n">
-        <v>3</v>
-      </c>
-      <c r="N94" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>1</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
       <c r="U94" t="n">
         <v>0</v>
       </c>
@@ -13650,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X94" t="n">
         <v>0</v>
@@ -13662,12 +13660,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Joao Mario</t>
+          <t>Ranieri L.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -13679,10 +13677,10 @@
         <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
@@ -13690,34 +13688,36 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>57.8</v>
+        <v>56.9</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K95" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="L95" t="n">
         <v>5.79</v>
       </c>
-      <c r="L95" t="n">
-        <v>6</v>
-      </c>
       <c r="M95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="O95" t="n">
-        <v>0.368</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
@@ -13735,10 +13735,10 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
@@ -13747,21 +13747,21 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ranieri L.</t>
+          <t>Haps</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
         <v>10</v>
@@ -13775,7 +13775,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>56.9</v>
+        <v>56</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -13783,49 +13783,49 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K96" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="L96" t="n">
-        <v>5.79</v>
+        <v>5.98</v>
       </c>
       <c r="M96" t="n">
+        <v>2</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
         <v>3</v>
       </c>
-      <c r="N96" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="P96" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>1</v>
-      </c>
-      <c r="T96" t="n">
-        <v>5</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>8</v>
-      </c>
       <c r="X96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
@@ -13834,27 +13834,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Haps</t>
+          <t>Tomori</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>56</v>
+        <v>55.7</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -13870,25 +13870,25 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K97" t="n">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="L97" t="n">
-        <v>5.98</v>
+        <v>5.88</v>
       </c>
       <c r="M97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N97" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="O97" t="n">
-        <v>0.474</v>
+        <v>0.658</v>
       </c>
       <c r="P97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>1</v>
@@ -13897,10 +13897,10 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -13909,10 +13909,10 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
@@ -13921,27 +13921,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tomori</t>
+          <t>Tavares N.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
@@ -13949,36 +13949,36 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>55.7</v>
+        <v>54.2</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K98" t="n">
-        <v>5.97</v>
+        <v>5.91</v>
       </c>
       <c r="L98" t="n">
-        <v>5.88</v>
+        <v>5.8</v>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N98" t="n">
-        <v>-0.12</v>
+        <v>-0.7</v>
       </c>
       <c r="O98" t="n">
-        <v>0.658</v>
+        <v>0.592</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
@@ -13996,10 +13996,10 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
         <v>12</v>
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E116" t="n">
         <v>12</v>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E117" t="n">
         <v>12</v>
@@ -15989,7 +15989,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Marin R.</t>
+          <t>Schingtienne</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
@@ -16017,28 +16017,28 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>24.8</v>
+        <v>17.2</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K122" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L122" t="n">
-        <v>5.83</v>
+        <v>5.63</v>
       </c>
       <c r="M122" t="n">
         <v>1</v>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="n">
-        <v>0.079</v>
+        <v>0.395</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         <v>1</v>
       </c>
       <c r="T122" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -16062,7 +16062,7 @@
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X122" t="n">
         <v>0</v>
@@ -16074,7 +16074,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Schingtienne</t>
+          <t>Palma</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -16084,17 +16084,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D123" t="n">
         <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>17.2</v>
+        <v>15.1</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -16110,20 +16110,20 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K123" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L123" t="n">
-        <v>5.63</v>
+        <v>5.5</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
-        <v>0.395</v>
+        <v>0.105</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
@@ -16138,7 +16138,7 @@
         <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -16147,7 +16147,7 @@
         <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X123" t="n">
         <v>0</v>
@@ -16159,7 +16159,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Palma</t>
+          <t>Lucchesi</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -16169,14 +16169,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E124" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F124" t="n">
         <v>6</v>
@@ -16187,7 +16187,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>15.1</v>
+        <v>11.2</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -16195,20 +16195,20 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
         <v>1</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -16223,7 +16223,7 @@
         <v>1</v>
       </c>
       <c r="T124" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -16244,7 +16244,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lucchesi</t>
+          <t>Odenthal</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -16254,17 +16254,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>8</v>
+      </c>
+      <c r="F125" t="n">
         <v>4</v>
-      </c>
-      <c r="E125" t="n">
-        <v>12</v>
-      </c>
-      <c r="F125" t="n">
-        <v>6</v>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -16308,10 +16308,10 @@
         <v>1</v>
       </c>
       <c r="T125" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="U125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -16343,7 +16343,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
         <v>12</v>
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
         <v>10</v>
@@ -16623,17 +16623,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Leysen F.</t>
+          <t>Correia T.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -16667,7 +16667,7 @@
         <v>1</v>
       </c>
       <c r="T130" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -16684,21 +16684,21 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Calvani</t>
+          <t>Leysen F.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E131" t="n">
         <v>12</v>
@@ -16728,7 +16728,7 @@
         <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -16745,27 +16745,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mitaj</t>
+          <t>Calvani</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>4</v>
       </c>
       <c r="E132" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
@@ -16786,10 +16786,10 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -16806,27 +16806,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Delli Carri</t>
+          <t>Mitaj</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>4</v>
       </c>
       <c r="E133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Comert</t>
+          <t>Delli Carri</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -16877,14 +16877,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D134" t="n">
         <v>4</v>
       </c>
       <c r="E134" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F134" t="n">
         <v>6</v>
@@ -16928,7 +16928,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Halhal</t>
+          <t>Comert</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -16938,17 +16938,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D135" t="n">
         <v>4</v>
       </c>
       <c r="E135" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
@@ -16989,12 +16989,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Correia T.</t>
+          <t>Halhal</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -17006,10 +17006,10 @@
         <v>4</v>
       </c>
       <c r="E136" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
@@ -17030,10 +17030,10 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E150" t="n">
         <v>5</v>
@@ -18473,7 +18473,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Casale</t>
+          <t>Marin R.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -18483,48 +18483,46 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E154" t="n">
+        <v>8</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4</v>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
         <v>3</v>
       </c>
-      <c r="E154" t="n">
-        <v>5</v>
-      </c>
-      <c r="F154" t="n">
-        <v>2</v>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H154" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J154" t="n">
-        <v>10</v>
-      </c>
       <c r="K154" t="n">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="L154" t="n">
-        <v>5.65</v>
+        <v>5.83</v>
       </c>
       <c r="M154" t="n">
-        <v>3</v>
-      </c>
-      <c r="N154" t="n">
-        <v>0.11</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="n">
-        <v>0.386</v>
+        <v>0.079</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -18536,10 +18534,10 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -18548,7 +18546,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X154" t="n">
         <v>0</v>
@@ -18560,27 +18558,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Candè</t>
+          <t>Casale</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D155" t="n">
         <v>3</v>
       </c>
       <c r="E155" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F155" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
@@ -18588,7 +18586,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -18596,22 +18594,22 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K155" t="n">
-        <v>5.69</v>
+        <v>5.65</v>
       </c>
       <c r="L155" t="n">
-        <v>5.56</v>
+        <v>5.65</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N155" t="n">
-        <v>-0.26</v>
+        <v>0.11</v>
       </c>
       <c r="O155" t="n">
-        <v>0.329</v>
+        <v>0.386</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -18635,7 +18633,7 @@
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X155" t="n">
         <v>0</v>
@@ -18647,35 +18645,35 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Candè</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
+        <v>7</v>
+      </c>
+      <c r="F156" t="n">
         <v>4</v>
       </c>
-      <c r="F156" t="n">
-        <v>2</v>
-      </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -18683,22 +18681,22 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K156" t="n">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="L156" t="n">
-        <v>5.7</v>
+        <v>5.56</v>
       </c>
       <c r="M156" t="n">
         <v>2</v>
       </c>
       <c r="N156" t="n">
-        <v>-0.05</v>
+        <v>-0.26</v>
       </c>
       <c r="O156" t="n">
-        <v>0.303</v>
+        <v>0.329</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -18722,7 +18720,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X156" t="n">
         <v>0</v>
@@ -18734,7 +18732,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Moreno M.</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -18744,46 +18742,48 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D157" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" t="n">
+        <v>4</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
         <v>5</v>
       </c>
-      <c r="E157" t="n">
-        <v>6</v>
-      </c>
-      <c r="F157" t="n">
-        <v>3</v>
-      </c>
-      <c r="G157" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H157" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J157" t="n">
-        <v>3</v>
-      </c>
       <c r="K157" t="n">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="L157" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
-      </c>
-      <c r="N157" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N157" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="O157" t="n">
-        <v>0.079</v>
+        <v>0.303</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -18807,7 +18807,7 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X157" t="n">
         <v>0</v>
@@ -18819,27 +18819,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ndaba</t>
+          <t>Moreno M.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>16</v>
+        <v>16.9</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -18855,20 +18855,20 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K158" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L158" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M158" t="n">
         <v>1</v>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="n">
-        <v>0.237</v>
+        <v>0.079</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -18880,10 +18880,10 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>
@@ -18904,35 +18904,35 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Matturro</t>
+          <t>Ndaba</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
+        <v>5</v>
+      </c>
+      <c r="F159" t="n">
         <v>2</v>
       </c>
-      <c r="F159" t="n">
-        <v>1</v>
-      </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -18940,22 +18940,20 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K159" t="n">
-        <v>5.62</v>
+        <v>5.5</v>
       </c>
       <c r="L159" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="M159" t="n">
-        <v>2</v>
-      </c>
-      <c r="N159" t="n">
-        <v>0.71</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="n">
-        <v>0.197</v>
+        <v>0.237</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -18967,10 +18965,10 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U159" t="n">
         <v>0</v>
@@ -18979,7 +18977,7 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X159" t="n">
         <v>0</v>
@@ -18991,82 +18989,82 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Carboni F.</t>
+          <t>Matturro</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D160" t="n">
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>12</v>
+      </c>
+      <c r="K160" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="L160" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="M160" t="n">
         <v>2</v>
       </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H160" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J160" t="n">
+      <c r="N160" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" t="n">
         <v>2</v>
-      </c>
-      <c r="K160" t="n">
-        <v>6</v>
-      </c>
-      <c r="L160" t="n">
-        <v>6</v>
-      </c>
-      <c r="M160" t="n">
-        <v>3</v>
-      </c>
-      <c r="N160" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O160" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" t="n">
-        <v>0</v>
-      </c>
-      <c r="U160" t="n">
-        <v>0</v>
-      </c>
-      <c r="V160" t="n">
-        <v>0</v>
-      </c>
-      <c r="W160" t="n">
-        <v>0</v>
       </c>
       <c r="X160" t="n">
         <v>0</v>
@@ -19078,17 +19076,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mlacic</t>
+          <t>Carboni F.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -19106,7 +19104,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -19114,20 +19112,22 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>2</v>
+      </c>
+      <c r="K161" t="n">
+        <v>6</v>
+      </c>
+      <c r="L161" t="n">
+        <v>6</v>
+      </c>
+      <c r="M161" t="n">
         <v>3</v>
       </c>
-      <c r="K161" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="L161" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M161" t="n">
-        <v>1</v>
-      </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>2.44</v>
+      </c>
       <c r="O161" t="n">
-        <v>0.079</v>
+        <v>0.061</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -19151,7 +19151,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X161" t="n">
         <v>0</v>
@@ -19163,7 +19163,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ndiaye</t>
+          <t>Mlacic</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -19173,17 +19173,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D162" t="n">
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F162" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -19199,20 +19199,20 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K162" t="n">
-        <v>5.59</v>
+        <v>5.83</v>
       </c>
       <c r="L162" t="n">
-        <v>5.36</v>
+        <v>5.67</v>
       </c>
       <c r="M162" t="n">
         <v>1</v>
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="n">
-        <v>0.289</v>
+        <v>0.079</v>
       </c>
       <c r="P162" t="n">
         <v>0</v>
@@ -19224,10 +19224,10 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T162" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -19236,10 +19236,10 @@
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y162" t="inlineStr"/>
       <c r="Z162" t="inlineStr"/>
@@ -19248,7 +19248,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Otoa</t>
+          <t>Ndiaye</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -19258,17 +19258,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D163" t="n">
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -19284,22 +19284,20 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K163" t="n">
-        <v>5.6</v>
+        <v>5.59</v>
       </c>
       <c r="L163" t="n">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
       <c r="M163" t="n">
-        <v>2</v>
-      </c>
-      <c r="N163" t="n">
-        <v>0.68</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="n">
-        <v>0.171</v>
+        <v>0.289</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -19314,7 +19312,7 @@
         <v>1</v>
       </c>
       <c r="T163" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -19323,10 +19321,10 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y163" t="inlineStr"/>
       <c r="Z163" t="inlineStr"/>
@@ -19335,7 +19333,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Odenthal</t>
+          <t>Otoa</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -19345,17 +19343,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
@@ -19371,20 +19369,22 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
-      </c>
-      <c r="N164" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0.68</v>
+      </c>
       <c r="O164" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -19399,16 +19399,16 @@
         <v>1</v>
       </c>
       <c r="T164" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="U164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X164" t="n">
         <v>0</v>
@@ -19749,27 +19749,27 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Franjic</t>
+          <t>Bakoune</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D170" t="n">
         <v>2</v>
       </c>
       <c r="E170" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>1</v>
       </c>
       <c r="T170" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U170" t="n">
         <v>0</v>
@@ -19810,27 +19810,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Aurelio</t>
+          <t>Franjic</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>2</v>
       </c>
       <c r="E171" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
@@ -19851,10 +19851,10 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U171" t="n">
         <v>0</v>
@@ -19871,27 +19871,27 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Oyono J.</t>
+          <t>Aurelio</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E172" t="n">
+        <v>5</v>
+      </c>
+      <c r="F172" t="n">
         <v>2</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1</v>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Bakoune</t>
+          <t>Cinquegrano</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -19942,11 +19942,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
         <v>4</v>
@@ -19976,7 +19976,7 @@
         <v>1</v>
       </c>
       <c r="T173" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U173" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Cinquegrano</t>
+          <t>Oyono J.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -20003,17 +20003,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D174" t="n">
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
@@ -20034,10 +20034,10 @@
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -21033,7 +21033,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
         <v>247</v>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
         <v>160</v>
@@ -21294,7 +21294,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
         <v>236</v>
@@ -21381,7 +21381,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
         <v>192</v>
@@ -21468,7 +21468,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
         <v>145</v>
@@ -21640,7 +21640,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
         <v>107</v>
@@ -21873,7 +21873,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>75</v>
@@ -22395,7 +22395,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>45</v>
@@ -22741,7 +22741,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>45</v>
@@ -22913,7 +22913,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
         <v>86</v>
@@ -23520,7 +23520,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
         <v>68</v>
@@ -23607,7 +23607,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
         <v>40</v>
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
         <v>44</v>
@@ -24711,7 +24711,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
         <v>30</v>
@@ -24885,7 +24885,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
         <v>22</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
         <v>23</v>
@@ -26882,7 +26882,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
         <v>22</v>
@@ -27056,7 +27056,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
         <v>20</v>
@@ -27400,7 +27400,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
         <v>25</v>
@@ -27534,7 +27534,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Calò</t>
+          <t>Romano</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -27544,17 +27544,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>7</v>
       </c>
       <c r="E79" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
@@ -27578,10 +27578,10 @@
         <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -27595,7 +27595,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Oulai</t>
+          <t>Calò</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -27605,17 +27605,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E80" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -27656,7 +27656,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Romano</t>
+          <t>Milla</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -27666,11 +27666,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E81" t="n">
         <v>20</v>
@@ -27700,10 +27700,10 @@
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -27717,7 +27717,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Milla</t>
+          <t>Oulai</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -27727,11 +27727,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
         <v>20</v>
@@ -27761,7 +27761,7 @@
         <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -28288,7 +28288,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E89" t="n">
         <v>17</v>
@@ -28806,7 +28806,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E95" t="n">
         <v>17</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
         <v>12</v>
@@ -29931,7 +29931,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E108" t="n">
         <v>15</v>
@@ -30018,7 +30018,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E109" t="n">
         <v>13</v>
@@ -30277,7 +30277,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E112" t="n">
         <v>14</v>
@@ -30623,7 +30623,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E116" t="n">
         <v>12</v>
@@ -30797,7 +30797,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E118" t="n">
         <v>12</v>
@@ -30882,7 +30882,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
         <v>15</v>
@@ -31224,7 +31224,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E123" t="n">
         <v>16</v>
@@ -31311,7 +31311,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E124" t="n">
         <v>13</v>
@@ -31653,7 +31653,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E128" t="n">
         <v>11</v>
@@ -31738,7 +31738,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E129" t="n">
         <v>13</v>
@@ -31823,7 +31823,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130" t="n">
         <v>12</v>
@@ -32335,7 +32335,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E138" t="n">
         <v>12</v>
@@ -32483,7 +32483,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E140" t="n">
         <v>8</v>
@@ -33614,7 +33614,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E153" t="n">
         <v>8</v>
@@ -33788,7 +33788,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" t="n">
         <v>8</v>
@@ -34136,7 +34136,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" t="n">
         <v>5</v>
@@ -34482,7 +34482,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E163" t="n">
         <v>7</v>
@@ -34996,7 +34996,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E169" t="n">
         <v>5</v>
@@ -35667,7 +35667,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -36347,7 +36347,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
         <v>367</v>
@@ -36434,7 +36434,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
         <v>263</v>
@@ -36521,7 +36521,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
         <v>257</v>
@@ -36606,7 +36606,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="n">
         <v>414</v>
@@ -36752,7 +36752,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -36839,7 +36839,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
         <v>150</v>
@@ -37100,7 +37100,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
         <v>105</v>
@@ -37185,7 +37185,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
         <v>170</v>
@@ -37446,7 +37446,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" t="n">
         <v>211</v>
@@ -37618,7 +37618,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>95</v>
@@ -37778,17 +37778,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Castro S.</t>
+          <t>Raspadori</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -37806,33 +37806,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>61.1</v>
+        <v>60.1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>5.93</v>
+        <v>6.12</v>
       </c>
       <c r="L19" t="n">
-        <v>6.51</v>
+        <v>6.88</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="O19" t="n">
-        <v>0.64</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -37844,16 +37844,16 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -38314,7 +38314,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
@@ -38401,7 +38401,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
         <v>58</v>
@@ -38474,7 +38474,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pellegrino M.</t>
+          <t>Castro S.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -38484,17 +38484,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60.3</v>
+        <v>61.1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -38510,37 +38510,37 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>5.99</v>
+        <v>5.93</v>
       </c>
       <c r="L27" t="n">
-        <v>6.65</v>
+        <v>6.51</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.21</v>
+        <v>-0.15</v>
       </c>
       <c r="O27" t="n">
-        <v>0.632</v>
+        <v>0.64</v>
       </c>
       <c r="P27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -38561,27 +38561,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Raspadori</t>
+          <t>Pellegrino M.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
@@ -38589,54 +38589,54 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>60.1</v>
+        <v>60.3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K28" t="n">
-        <v>6.12</v>
+        <v>5.99</v>
       </c>
       <c r="L28" t="n">
-        <v>6.88</v>
+        <v>6.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.05</v>
+        <v>-0.21</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -41059,7 +41059,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
         <v>12</v>
@@ -42102,7 +42102,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
         <v>10</v>
@@ -42944,7 +42944,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Havel</t>
+          <t>Varela G.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -42954,14 +42954,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F81" t="n">
         <v>4</v>
@@ -42985,13 +42985,13 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -43005,27 +43005,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Robinson J.</t>
+          <t>Havel</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
@@ -43066,12 +43066,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Varela G.</t>
+          <t>Robinson J.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -43080,13 +43080,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
@@ -43107,13 +43107,13 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -43141,7 +43141,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
         <v>10</v>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33941,7 +33941,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -36118,7 +36118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA87"/>
+  <dimension ref="A1:AA88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -37735,27 +37735,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Simeone</t>
+          <t>Raspadori</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -37763,36 +37763,36 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="L19" t="n">
-        <v>7.09</v>
+        <v>6.88</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.09</v>
+        <v>-0.05</v>
       </c>
       <c r="O19" t="n">
-        <v>0.596</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -37801,16 +37801,16 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -37822,73 +37822,73 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Leao</t>
+          <t>Simeone</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>38</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
+        <v>40</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>1a Fascia</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>84.3</v>
+        <v>60.1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K20" t="n">
-        <v>5.88</v>
+        <v>6.08</v>
       </c>
       <c r="L20" t="n">
-        <v>6.86</v>
+        <v>7.09</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.33</v>
+        <v>1.09</v>
       </c>
       <c r="O20" t="n">
-        <v>0.833</v>
+        <v>0.596</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -37897,7 +37897,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Esposito Se.</t>
+          <t>Leao</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -37919,17 +37919,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -37937,39 +37937,39 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>77.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
-        <v>6.26</v>
+        <v>5.88</v>
       </c>
       <c r="L21" t="n">
-        <v>6.88</v>
+        <v>6.86</v>
       </c>
       <c r="M21" t="n">
         <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.64</v>
+        <v>-0.33</v>
       </c>
       <c r="O21" t="n">
-        <v>0.605</v>
+        <v>0.833</v>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -37984,7 +37984,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -37996,7 +37996,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Soulè</t>
+          <t>Esposito Se.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -38006,17 +38006,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -38024,54 +38024,54 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>76.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K22" t="n">
-        <v>6.12</v>
+        <v>6.26</v>
       </c>
       <c r="L22" t="n">
-        <v>6.83</v>
+        <v>6.88</v>
       </c>
       <c r="M22" t="n">
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.22</v>
+        <v>2.64</v>
       </c>
       <c r="O22" t="n">
-        <v>0.798</v>
+        <v>0.605</v>
       </c>
       <c r="P22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>6</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>6</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -38083,27 +38083,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pinamonti</t>
+          <t>Soulè</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>74.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -38119,37 +38119,37 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>5.88</v>
+        <v>6.12</v>
       </c>
       <c r="L23" t="n">
-        <v>6.62</v>
+        <v>6.83</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -38158,10 +38158,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
@@ -38170,27 +38170,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Adams C.</t>
+          <t>Pinamonti</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
@@ -38198,57 +38198,57 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K24" t="n">
-        <v>5.98</v>
+        <v>5.88</v>
       </c>
       <c r="L24" t="n">
-        <v>6.64</v>
+        <v>6.62</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.882</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="n">
         <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
@@ -38257,27 +38257,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dovbyk</t>
+          <t>Adams C.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
@@ -38285,37 +38285,37 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>5.98</v>
       </c>
       <c r="L25" t="n">
-        <v>6.77</v>
+        <v>6.64</v>
       </c>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.42</v>
+        <v>-0.12</v>
       </c>
       <c r="O25" t="n">
-        <v>0.592</v>
+        <v>0.882</v>
       </c>
       <c r="P25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -38323,10 +38323,10 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -38344,7 +38344,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Castro S.</t>
+          <t>Dovbyk</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -38354,17 +38354,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>61.8</v>
+        <v>64</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -38380,26 +38380,26 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>6.51</v>
+        <v>6.77</v>
       </c>
       <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="P26" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P26" t="n">
-        <v>7</v>
-      </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
@@ -38410,7 +38410,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -38419,7 +38419,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -38431,7 +38431,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pellegrino M.</t>
+          <t>Castro S.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -38441,17 +38441,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60.6</v>
+        <v>61.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -38467,37 +38467,37 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>5.99</v>
+        <v>5.93</v>
       </c>
       <c r="L27" t="n">
-        <v>6.65</v>
+        <v>6.51</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.21</v>
+        <v>-0.15</v>
       </c>
       <c r="O27" t="n">
-        <v>0.632</v>
+        <v>0.64</v>
       </c>
       <c r="P27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -38506,7 +38506,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -38518,27 +38518,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Raspadori</t>
+          <t>Pellegrino M.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -38554,46 +38554,46 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K28" t="n">
-        <v>6.12</v>
+        <v>5.99</v>
       </c>
       <c r="L28" t="n">
-        <v>6.88</v>
+        <v>6.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.05</v>
+        <v>-0.21</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -41605,71 +41605,51 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Frigan</t>
+          <t>Geubbels</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
-      <c r="H65" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -41677,12 +41657,8 @@
       <c r="V65" t="n">
         <v>0</v>
       </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
@@ -41690,7 +41666,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Geubbels</t>
+          <t>Rrahmani Al.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -41700,17 +41676,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D66" t="n">
+        <v>8</v>
+      </c>
+      <c r="E66" t="n">
+        <v>18</v>
+      </c>
+      <c r="F66" t="n">
         <v>9</v>
-      </c>
-      <c r="E66" t="n">
-        <v>23</v>
-      </c>
-      <c r="F66" t="n">
-        <v>12</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
@@ -41731,10 +41707,10 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -41751,7 +41727,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Rrahmani Al.</t>
+          <t>Adorante</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -41765,13 +41741,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F67" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
@@ -41812,27 +41788,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Adorante</t>
+          <t>Fatah</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
@@ -42816,60 +42792,84 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Varela G.</t>
+          <t>Frigan</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
       </c>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
@@ -42877,7 +42877,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Havel</t>
+          <t>Varela G.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -42887,14 +42887,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F81" t="n">
         <v>4</v>
@@ -42918,13 +42918,13 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -42938,27 +42938,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Robinson J.</t>
+          <t>Havel</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Lontani</t>
+          <t>Robinson J.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -43009,11 +43009,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -43040,10 +43040,10 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -43060,73 +43060,51 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azon</t>
+          <t>Lontani</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>2</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -43134,12 +43112,8 @@
       <c r="V84" t="n">
         <v>0</v>
       </c>
-      <c r="W84" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0</v>
-      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
@@ -43147,17 +43121,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lisman</t>
+          <t>Azon</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -43174,19 +43148,41 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
       <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
       <c r="S85" t="n">
         <v>0</v>
       </c>
@@ -43199,8 +43195,12 @@
       <c r="V85" t="n">
         <v>0</v>
       </c>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
@@ -43208,12 +43208,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Lauberbach</t>
+          <t>Lisman</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -43269,7 +43269,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>De Martis</t>
+          <t>Lauberbach</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -43279,7 +43279,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -43327,8 +43327,69 @@
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>De Martis</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pc</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA87"/>
+  <autoFilter ref="A1:AA88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>6.75</v>
+        <v>6.17</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>6.25</v>
+        <v>5.83</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -965,10 +965,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1200,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1872,10 +1872,10 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -5959,16 +5959,16 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>3</v>
@@ -6046,10 +6046,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>7</v>
+        <v>6.33</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -6218,10 +6218,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>7.25</v>
+        <v>7.17</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -6392,10 +6392,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
         <v>6</v>
@@ -6540,10 +6540,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -6627,13 +6627,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -6714,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>8.25</v>
+        <v>7.67</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
@@ -6801,16 +6801,16 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>5.75</v>
+        <v>6.17</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
@@ -6975,10 +6975,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -7149,10 +7149,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7234,16 +7234,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
         <v>4</v>
@@ -7408,10 +7408,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8803,10 +8803,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -9151,16 +9151,16 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
         <v>6</v>
@@ -9236,16 +9236,16 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>3.75</v>
+        <v>4.67</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
         <v>1</v>
@@ -9839,16 +9839,16 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" t="n">
         <v>6</v>
@@ -10274,10 +10274,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -10446,10 +10446,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -10968,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T61" t="n">
         <v>6</v>
@@ -11142,10 +11142,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T63" t="n">
-        <v>7.75</v>
+        <v>7.17</v>
       </c>
       <c r="U63" t="n">
         <v>1</v>
@@ -12370,10 +12370,10 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -12736,7 +12736,7 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T85" t="n">
         <v>5</v>
@@ -13920,10 +13920,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T99" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -14268,10 +14268,10 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T103" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -14355,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T104" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -14873,10 +14873,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T110" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -15733,10 +15733,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T120" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -16658,7 +16658,7 @@
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T131" t="n">
         <v>5.5</v>
@@ -16780,10 +16780,10 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -16963,10 +16963,10 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -17085,16 +17085,16 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T138" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
@@ -17329,10 +17329,10 @@
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T142" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -18620,10 +18620,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T157" t="n">
-        <v>5.25</v>
+        <v>5.17</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -21612,10 +21612,10 @@
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>9.75</v>
+        <v>8.5</v>
       </c>
       <c r="U5" t="n">
         <v>2</v>
@@ -21956,10 +21956,10 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
@@ -22021,10 +22021,10 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
@@ -22191,10 +22191,10 @@
         <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -22365,10 +22365,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -22887,10 +22887,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -22974,13 +22974,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>5.25</v>
+        <v>6.67</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -23146,10 +23146,10 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>8.25</v>
+        <v>7.67</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
@@ -23318,10 +23318,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -23492,13 +23492,13 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>5.75</v>
+        <v>7.17</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -23664,10 +23664,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -23838,10 +23838,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
@@ -24010,10 +24010,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -24075,7 +24075,7 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
         <v>6</v>
@@ -24319,10 +24319,10 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -24550,13 +24550,13 @@
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25151,7 +25151,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
         <v>5.5</v>
@@ -25238,10 +25238,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>6.25</v>
+        <v>5.67</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -25673,10 +25673,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -26280,10 +26280,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T61" t="n">
-        <v>6.5</v>
+        <v>6.17</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -26367,10 +26367,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T62" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -26454,7 +26454,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" t="n">
         <v>5.5</v>
@@ -26541,10 +26541,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T64" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -26887,10 +26887,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>11.5</v>
+        <v>8.25</v>
       </c>
       <c r="U68" t="n">
         <v>1</v>
@@ -27235,10 +27235,10 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T72" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -27409,10 +27409,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T74" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -27583,10 +27583,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T76" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -27668,7 +27668,7 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T77" t="n">
         <v>6.5</v>
@@ -28334,10 +28334,10 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -28765,10 +28765,10 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T92" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -31106,10 +31106,10 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T119" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -32637,10 +32637,10 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T138" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -32820,10 +32820,10 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T141" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -37140,13 +37140,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -37227,13 +37227,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>5.5</v>
+        <v>7.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -37312,13 +37312,13 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -37397,10 +37397,10 @@
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>15.5</v>
+        <v>12.33</v>
       </c>
       <c r="U5" t="n">
         <v>5</v>
@@ -37545,10 +37545,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -37719,10 +37719,10 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -37978,10 +37978,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
@@ -38324,16 +38324,16 @@
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -38498,10 +38498,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -38733,16 +38733,16 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>9.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
@@ -38907,13 +38907,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -39081,10 +39081,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -39255,13 +39255,13 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>4.5</v>
+        <v>6.17</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -39342,10 +39342,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -39514,7 +39514,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
         <v>6</v>
@@ -39945,10 +39945,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -40744,10 +40744,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -41090,10 +41090,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T50" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -42222,10 +42222,10 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -2275,10 +2275,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>4.25</v>
+        <v>4.83</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2706,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>5.75</v>
+        <v>5.17</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3004,10 +3004,10 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -7669,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -7841,10 +7841,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -8274,10 +8274,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -11401,10 +11401,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T66" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -11830,10 +11830,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T71" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -12248,10 +12248,10 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T77" t="n">
-        <v>8.5</v>
+        <v>7.67</v>
       </c>
       <c r="U77" t="n">
         <v>1</v>
@@ -12309,16 +12309,16 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T78" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -12797,10 +12797,10 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T86" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -12965,10 +12965,10 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T88" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -13400,16 +13400,16 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T93" t="n">
-        <v>5.75</v>
+        <v>6.33</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T102" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -14614,10 +14614,10 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T107" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -14788,10 +14788,10 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T113" t="n">
         <v>6</v>
@@ -16079,16 +16079,16 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T124" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" t="n">
         <v>4</v>
@@ -16251,10 +16251,10 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T126" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -16421,10 +16421,10 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T128" t="n">
-        <v>4.75</v>
+        <v>5.33</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -17207,10 +17207,10 @@
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T140" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -18535,10 +18535,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T156" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -19138,10 +19138,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T163" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -19652,13 +19652,13 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -27907,10 +27907,10 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T80" t="n">
-        <v>6.75</v>
+        <v>6.67</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -27968,7 +27968,7 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T81" t="n">
         <v>5.5</v>
@@ -28591,10 +28591,10 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T90" t="n">
-        <v>7.25</v>
+        <v>6.83</v>
       </c>
       <c r="U90" t="n">
         <v>1</v>
@@ -30155,10 +30155,10 @@
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T108" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -30240,16 +30240,16 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T109" t="n">
-        <v>5.75</v>
+        <v>6.17</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" t="n">
         <v>4</v>
@@ -30412,10 +30412,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T111" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -30760,7 +30760,7 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T115" t="n">
         <v>5.5</v>
@@ -30932,10 +30932,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T117" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -31019,10 +31019,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T118" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -31620,10 +31620,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T125" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -32304,7 +32304,7 @@
         <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T133" t="n">
         <v>6</v>
@@ -32881,10 +32881,10 @@
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T142" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -33578,10 +33578,10 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -34361,16 +34361,16 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T160" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="U160" t="n">
         <v>0</v>
       </c>
       <c r="V160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W160" t="n">
         <v>5</v>
@@ -34620,10 +34620,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T163" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -35926,10 +35926,10 @@
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U179" t="n">
         <v>0</v>
@@ -35987,10 +35987,10 @@
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T180" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U180" t="n">
         <v>0</v>
@@ -36336,10 +36336,10 @@
         <v>0</v>
       </c>
       <c r="S185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T185" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U185" t="n">
         <v>0</v>
@@ -39860,10 +39860,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -40032,13 +40032,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>9.5</v>
+        <v>10.83</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -40158,7 +40158,7 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
         <v>5.5</v>
@@ -40219,10 +40219,10 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -41519,13 +41519,13 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -41950,10 +41950,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -42035,13 +42035,13 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T61" t="n">
-        <v>7.25</v>
+        <v>8.17</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61" t="n">
         <v>1</v>
@@ -42161,10 +42161,10 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -42466,13 +42466,13 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -42634,10 +42634,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -43320,10 +43320,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -43507,13 +43507,13 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -43836,10 +43836,10 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$191</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$193</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$87</definedName>
   </definedNames>
@@ -5724,7 +5724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA190"/>
+  <dimension ref="A1:AA191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11166,82 +11166,82 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Olivera</t>
+          <t>Marcandalli</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D64" t="n">
+        <v>6</v>
+      </c>
+      <c r="E64" t="n">
+        <v>14</v>
+      </c>
+      <c r="F64" t="n">
+        <v>7</v>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>38</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>31</v>
+      </c>
+      <c r="K64" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="L64" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
         <v>4</v>
-      </c>
-      <c r="E64" t="n">
-        <v>13</v>
-      </c>
-      <c r="F64" t="n">
-        <v>6</v>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>22</v>
-      </c>
-      <c r="K64" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L64" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3</v>
-      </c>
-      <c r="N64" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="T64" t="n">
-        <v>5</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>3</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
@@ -11253,21 +11253,21 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marcandalli</t>
+          <t>Kouadio</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
         <v>14</v>
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -11289,28 +11289,26 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>5.87</v>
+        <v>6</v>
       </c>
       <c r="L65" t="n">
-        <v>5.84</v>
+        <v>6</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0.09</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
-        <v>0.513</v>
+        <v>0.026</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -11319,7 +11317,7 @@
         <v>3</v>
       </c>
       <c r="T65" t="n">
-        <v>5.33</v>
+        <v>5.67</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -11328,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -11340,27 +11338,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kouadio</t>
+          <t>Provstgaard</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
@@ -11368,7 +11366,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>37.3</v>
+        <v>36.7</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -11376,20 +11374,22 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K66" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="L66" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="O66" t="n">
-        <v>0.026</v>
+        <v>0.316</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -11413,7 +11413,7 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
@@ -11425,27 +11425,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Provstgaard</t>
+          <t>Heggem</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>36.7</v>
+        <v>33.8</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -11461,22 +11461,20 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K67" t="n">
-        <v>5.91</v>
+        <v>5.84</v>
       </c>
       <c r="L67" t="n">
-        <v>5.85</v>
+        <v>5.8</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-0.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>0.316</v>
+        <v>0.658</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -11491,7 +11489,7 @@
         <v>3</v>
       </c>
       <c r="T67" t="n">
-        <v>5.67</v>
+        <v>5.17</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -11500,10 +11498,10 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
@@ -11512,7 +11510,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Heggem</t>
+          <t>Rodriguez Ju.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -11522,17 +11520,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
@@ -11540,7 +11538,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -11548,23 +11546,23 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K68" t="n">
-        <v>5.84</v>
+        <v>5.62</v>
       </c>
       <c r="L68" t="n">
-        <v>5.8</v>
+        <v>5.72</v>
       </c>
       <c r="M68" t="n">
         <v>1</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
-        <v>0.658</v>
+        <v>0.421</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11576,7 +11574,7 @@
         <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>5.17</v>
+        <v>6.17</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -11585,10 +11583,10 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
@@ -11597,59 +11595,61 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Rodriguez Ju.</t>
+          <t>Jimenez A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D69" t="n">
+        <v>7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>17</v>
+      </c>
+      <c r="F69" t="n">
+        <v>8</v>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L69" t="n">
         <v>5</v>
       </c>
-      <c r="E69" t="n">
-        <v>14</v>
-      </c>
-      <c r="F69" t="n">
-        <v>7</v>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>16</v>
-      </c>
-      <c r="K69" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="L69" t="n">
-        <v>5.72</v>
-      </c>
       <c r="M69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-0.33</v>
+      </c>
       <c r="O69" t="n">
-        <v>0.421</v>
+        <v>0.202</v>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11658,10 +11658,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T69" t="n">
-        <v>6.17</v>
+        <v>4.75</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -11670,7 +11670,7 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X69" t="n">
         <v>0</v>
@@ -11682,35 +11682,35 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jimenez A.</t>
+          <t>Troilo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D70" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>14</v>
+      </c>
+      <c r="F70" t="n">
         <v>7</v>
       </c>
-      <c r="E70" t="n">
-        <v>17</v>
-      </c>
-      <c r="F70" t="n">
-        <v>8</v>
-      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>31.3</v>
+        <v>30.1</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -11718,49 +11718,47 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K70" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="L70" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3</v>
+      </c>
+      <c r="T70" t="n">
         <v>5.5</v>
       </c>
-      <c r="L70" t="n">
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
         <v>5</v>
       </c>
-      <c r="M70" t="n">
-        <v>3</v>
-      </c>
-      <c r="N70" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>2</v>
-      </c>
-      <c r="T70" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1</v>
-      </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
@@ -11769,27 +11767,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Troilo</t>
+          <t>Zè Pedro</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
@@ -11797,7 +11795,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>30.1</v>
+        <v>26.9</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -11805,26 +11803,26 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K71" t="n">
-        <v>5.79</v>
+        <v>5.77</v>
       </c>
       <c r="L71" t="n">
-        <v>5.71</v>
+        <v>5.68</v>
       </c>
       <c r="M71" t="n">
         <v>1</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
-        <v>0.553</v>
+        <v>0.579</v>
       </c>
       <c r="P71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -11833,7 +11831,7 @@
         <v>3</v>
       </c>
       <c r="T71" t="n">
-        <v>5.5</v>
+        <v>5.83</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -11842,10 +11840,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
@@ -11854,21 +11852,21 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Zè Pedro</t>
+          <t>Bella-Kotchap</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
         <v>13</v>
@@ -11882,7 +11880,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>26.9</v>
+        <v>24.9</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -11890,35 +11888,35 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K72" t="n">
-        <v>5.77</v>
+        <v>5.83</v>
       </c>
       <c r="L72" t="n">
-        <v>5.68</v>
+        <v>5.75</v>
       </c>
       <c r="M72" t="n">
         <v>1</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
-        <v>0.579</v>
+        <v>0.474</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T72" t="n">
-        <v>5.83</v>
+        <v>5</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -11927,7 +11925,7 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X72" t="n">
         <v>0</v>
@@ -11939,84 +11937,60 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bella-Kotchap</t>
+          <t>Bracaglia</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
-      <c r="H73" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>18</v>
-      </c>
-      <c r="K73" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="L73" t="n">
-        <v>5.75</v>
-      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T73" t="n">
-        <v>5</v>
+        <v>7.67</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>3</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
@@ -12024,17 +11998,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bracaglia</t>
+          <t>Doekhi</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -12068,10 +12042,10 @@
         <v>3</v>
       </c>
       <c r="T74" t="n">
-        <v>7.67</v>
+        <v>6.67</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
         <v>1</v>
@@ -12085,7 +12059,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Doekhi</t>
+          <t>Koulierakis</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12095,14 +12069,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
         <v>8</v>
@@ -12126,16 +12100,16 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
@@ -12146,27 +12120,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Koulierakis</t>
+          <t>Theate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>8</v>
       </c>
       <c r="E76" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
@@ -12190,7 +12164,7 @@
         <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -12207,27 +12181,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Theate</t>
+          <t>Mangas</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D77" t="n">
+        <v>7</v>
+      </c>
+      <c r="E77" t="n">
+        <v>15</v>
+      </c>
+      <c r="F77" t="n">
         <v>8</v>
-      </c>
-      <c r="E77" t="n">
-        <v>20</v>
-      </c>
-      <c r="F77" t="n">
-        <v>10</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
@@ -12248,16 +12222,16 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T77" t="n">
-        <v>5.5</v>
+        <v>6.67</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -12268,7 +12242,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mangas</t>
+          <t>Kaiki</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12278,17 +12252,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -12309,16 +12283,16 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -12329,17 +12303,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kaiki</t>
+          <t>Calvani</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -12370,10 +12344,10 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -12390,27 +12364,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Calvani</t>
+          <t>Pedraza</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -12431,10 +12405,10 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T80" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -12451,27 +12425,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Pedraza</t>
+          <t>Badiashile</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>6</v>
       </c>
       <c r="E81" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -12492,10 +12466,10 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -12512,7 +12486,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Badiashile</t>
+          <t>Sutalo J.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -12522,17 +12496,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
@@ -12553,10 +12527,10 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -12573,27 +12547,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sutalo J.</t>
+          <t>Sugawara</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -12634,27 +12608,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sugawara</t>
+          <t>Leite</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
@@ -14725,74 +14699,74 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Valenti</t>
+          <t>Olivera</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>4</v>
       </c>
       <c r="E109" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F109" t="n">
+        <v>6</v>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>22</v>
+      </c>
+      <c r="K109" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L109" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="M109" t="n">
+        <v>3</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="n">
         <v>5</v>
       </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>27</v>
-      </c>
-      <c r="K109" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="L109" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="M109" t="n">
-        <v>2</v>
-      </c>
-      <c r="N109" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="n">
-        <v>1</v>
-      </c>
-      <c r="T109" t="n">
-        <v>6</v>
-      </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
@@ -14800,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X109" t="n">
         <v>0</v>
@@ -14812,27 +14786,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Fortini</t>
+          <t>Valenti</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
@@ -14840,7 +14814,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>38.2</v>
+        <v>39.4</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -14848,20 +14822,22 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K110" t="n">
         <v>5.96</v>
       </c>
       <c r="L110" t="n">
-        <v>5.96</v>
+        <v>5.83</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
-      </c>
-      <c r="N110" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N110" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="O110" t="n">
-        <v>0.316</v>
+        <v>0.618</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
@@ -14873,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T110" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -14885,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X110" t="n">
         <v>0</v>
@@ -14897,21 +14873,21 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Siebert</t>
+          <t>Fortini</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
         <v>12</v>
@@ -14925,7 +14901,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>37</v>
+        <v>38.2</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -14933,23 +14909,23 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K111" t="n">
-        <v>5.68</v>
+        <v>5.96</v>
       </c>
       <c r="L111" t="n">
-        <v>5.76</v>
+        <v>5.96</v>
       </c>
       <c r="M111" t="n">
         <v>1</v>
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
-        <v>0.5</v>
+        <v>0.316</v>
       </c>
       <c r="P111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -14961,7 +14937,7 @@
         <v>3</v>
       </c>
       <c r="T111" t="n">
-        <v>5.33</v>
+        <v>6.17</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -14970,7 +14946,7 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
         <v>0</v>
@@ -14982,27 +14958,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Doig</t>
+          <t>Siebert</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E112" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
@@ -15010,7 +14986,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>35.8</v>
+        <v>37</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -15018,25 +14994,23 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K112" t="n">
-        <v>5.85</v>
+        <v>5.68</v>
       </c>
       <c r="L112" t="n">
         <v>5.76</v>
       </c>
       <c r="M112" t="n">
-        <v>2</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-0.01</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
-        <v>0.724</v>
+        <v>0.5</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -15048,16 +15022,16 @@
         <v>3</v>
       </c>
       <c r="T112" t="n">
-        <v>7.17</v>
+        <v>5.33</v>
       </c>
       <c r="U112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X112" t="n">
         <v>0</v>
@@ -15069,21 +15043,21 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Britschgi</t>
+          <t>Doig</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E113" t="n">
         <v>10</v>
@@ -15105,38 +15079,40 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K113" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="L113" t="n">
-        <v>5.7</v>
+        <v>5.76</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
-      </c>
-      <c r="N113" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-0.01</v>
+      </c>
       <c r="O113" t="n">
-        <v>0.737</v>
+        <v>0.724</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T113" t="n">
-        <v>6</v>
+        <v>7.17</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -15145,7 +15121,7 @@
         <v>5</v>
       </c>
       <c r="X113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr"/>
@@ -15154,27 +15130,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Estupinan</t>
+          <t>Britschgi</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E114" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
@@ -15182,34 +15158,34 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K114" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="L114" t="n">
-        <v>5.71</v>
+        <v>5.7</v>
       </c>
       <c r="M114" t="n">
         <v>1</v>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="n">
-        <v>0.368</v>
+        <v>0.737</v>
       </c>
       <c r="P114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -15218,7 +15194,7 @@
         <v>2</v>
       </c>
       <c r="T114" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -15239,85 +15215,83 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Walukiewicz</t>
+          <t>Estupinan</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D115" t="n">
         <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F115" t="n">
+        <v>6</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>14</v>
+      </c>
+      <c r="K115" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="L115" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>2</v>
+      </c>
+      <c r="T115" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
         <v>5</v>
       </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>34</v>
-      </c>
-      <c r="K115" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="L115" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="M115" t="n">
-        <v>3</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>7</v>
-      </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
@@ -15326,21 +15300,21 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Floriani Mussolini</t>
+          <t>Walukiewicz</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
         <v>10</v>
@@ -15354,7 +15328,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>34.2</v>
+        <v>35.5</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -15362,20 +15336,22 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K116" t="n">
-        <v>5.72</v>
+        <v>5.81</v>
       </c>
       <c r="L116" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="M116" t="n">
-        <v>1</v>
-      </c>
-      <c r="N116" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O116" t="n">
-        <v>0.605</v>
+        <v>0.781</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
@@ -15387,10 +15363,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -15399,7 +15375,7 @@
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
@@ -15411,7 +15387,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Smolcic I.</t>
+          <t>Floriani Mussolini</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15421,7 +15397,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -15439,7 +15415,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>33.4</v>
+        <v>34.2</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -15447,22 +15423,20 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K117" t="n">
-        <v>5.96</v>
+        <v>5.72</v>
       </c>
       <c r="L117" t="n">
-        <v>5.84</v>
+        <v>5.72</v>
       </c>
       <c r="M117" t="n">
-        <v>2</v>
-      </c>
-      <c r="N117" t="n">
-        <v>0.09</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="n">
-        <v>0.434</v>
+        <v>0.605</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
@@ -15474,10 +15448,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T117" t="n">
-        <v>5.5</v>
+        <v>5.83</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -15486,7 +15460,7 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -15498,21 +15472,21 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Mazzocchi</t>
+          <t>Smolcic I.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E118" t="n">
         <v>10</v>
@@ -15526,7 +15500,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -15534,22 +15508,22 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K118" t="n">
-        <v>5.94</v>
+        <v>5.96</v>
       </c>
       <c r="L118" t="n">
-        <v>5.94</v>
+        <v>5.84</v>
       </c>
       <c r="M118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N118" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="O118" t="n">
-        <v>0.386</v>
+        <v>0.434</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -15561,10 +15535,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -15573,10 +15547,10 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
@@ -15585,21 +15559,21 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Vitik</t>
+          <t>Mazzocchi</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
         <v>10</v>
@@ -15613,7 +15587,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>32.9</v>
+        <v>33.2</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -15621,26 +15595,28 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K119" t="n">
         <v>5.94</v>
       </c>
       <c r="L119" t="n">
-        <v>5.86</v>
+        <v>5.94</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
-      </c>
-      <c r="N119" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.29</v>
+      </c>
       <c r="O119" t="n">
-        <v>0.474</v>
+        <v>0.386</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -15658,10 +15634,10 @@
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
@@ -15670,7 +15646,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ghilardi</t>
+          <t>Vitik</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15680,11 +15656,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E120" t="n">
         <v>10</v>
@@ -15698,7 +15674,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>32.4</v>
+        <v>32.9</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -15706,22 +15682,20 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K120" t="n">
-        <v>5.98</v>
+        <v>5.94</v>
       </c>
       <c r="L120" t="n">
-        <v>5.95</v>
+        <v>5.86</v>
       </c>
       <c r="M120" t="n">
-        <v>2</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0.41</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="n">
-        <v>0.592</v>
+        <v>0.474</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -15733,10 +15707,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -15745,7 +15719,7 @@
         <v>0</v>
       </c>
       <c r="W120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -15757,7 +15731,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Gaspar K.</t>
+          <t>Ghilardi</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -15767,17 +15741,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D121" t="n">
         <v>5</v>
       </c>
       <c r="E121" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
@@ -15785,27 +15759,27 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>31</v>
+        <v>32.4</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J121" t="n">
         <v>21</v>
       </c>
       <c r="K121" t="n">
-        <v>5.83</v>
+        <v>5.98</v>
       </c>
       <c r="L121" t="n">
-        <v>5.64</v>
+        <v>5.95</v>
       </c>
       <c r="M121" t="n">
         <v>2</v>
       </c>
       <c r="N121" t="n">
-        <v>-0.51</v>
+        <v>0.41</v>
       </c>
       <c r="O121" t="n">
         <v>0.592</v>
@@ -15820,10 +15794,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T121" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -15832,10 +15806,10 @@
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
@@ -15844,12 +15818,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Veiga D.</t>
+          <t>Gaspar K.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -15872,7 +15846,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>29.6</v>
+        <v>31</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -15880,22 +15854,22 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K122" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="L122" t="n">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
       </c>
       <c r="N122" t="n">
-        <v>-0.04</v>
+        <v>-0.51</v>
       </c>
       <c r="O122" t="n">
-        <v>0.618</v>
+        <v>0.592</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -15910,19 +15884,19 @@
         <v>3</v>
       </c>
       <c r="T122" t="n">
-        <v>5.83</v>
+        <v>5</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
@@ -15931,7 +15905,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Oyono A.</t>
+          <t>Veiga D.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -15941,17 +15915,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E123" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
@@ -15959,34 +15933,36 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>28.1</v>
+        <v>29.6</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="K123" t="n">
         <v>5.82</v>
       </c>
       <c r="L123" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="M123" t="n">
-        <v>1</v>
-      </c>
-      <c r="N123" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-0.04</v>
+      </c>
       <c r="O123" t="n">
-        <v>0.368</v>
+        <v>0.618</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
@@ -15995,7 +15971,7 @@
         <v>3</v>
       </c>
       <c r="T123" t="n">
-        <v>6.67</v>
+        <v>5.83</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -16004,7 +15980,7 @@
         <v>1</v>
       </c>
       <c r="W123" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X123" t="n">
         <v>0</v>
@@ -16016,21 +15992,21 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Juan Jesus</t>
+          <t>Oyono A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E124" t="n">
         <v>10</v>
@@ -16044,7 +16020,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>24.7</v>
+        <v>28.1</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -16052,49 +16028,47 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K124" t="n">
-        <v>5.86</v>
+        <v>5.82</v>
       </c>
       <c r="L124" t="n">
-        <v>5.62</v>
+        <v>5.75</v>
       </c>
       <c r="M124" t="n">
-        <v>3</v>
-      </c>
-      <c r="N124" t="n">
-        <v>-0.14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>0.509</v>
+        <v>0.368</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
@@ -16103,83 +16077,85 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cittadini</t>
+          <t>Juan Jesus</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D125" t="n">
         <v>4</v>
       </c>
       <c r="E125" t="n">
+        <v>10</v>
+      </c>
+      <c r="F125" t="n">
+        <v>5</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>21</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="L125" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="M125" t="n">
+        <v>3</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
         <v>8</v>
       </c>
-      <c r="F125" t="n">
-        <v>4</v>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>3</v>
-      </c>
-      <c r="K125" t="n">
-        <v>6</v>
-      </c>
-      <c r="L125" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="M125" t="n">
-        <v>1</v>
-      </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>3</v>
-      </c>
-      <c r="T125" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" t="n">
-        <v>1</v>
-      </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
@@ -16188,7 +16164,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Schingtienne</t>
+          <t>Cittadini</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -16198,17 +16174,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E126" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
@@ -16216,28 +16192,28 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>17</v>
+        <v>23.9</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K126" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L126" t="n">
-        <v>5.63</v>
+        <v>5.83</v>
       </c>
       <c r="M126" t="n">
         <v>1</v>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="n">
-        <v>0.395</v>
+        <v>0.079</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -16252,7 +16228,7 @@
         <v>3</v>
       </c>
       <c r="T126" t="n">
-        <v>5</v>
+        <v>5.83</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -16261,7 +16237,7 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X126" t="n">
         <v>0</v>
@@ -16273,7 +16249,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Palma</t>
+          <t>Schingtienne</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -16283,17 +16259,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
@@ -16301,7 +16277,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -16309,20 +16285,20 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K127" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L127" t="n">
-        <v>5.5</v>
+        <v>5.63</v>
       </c>
       <c r="M127" t="n">
         <v>1</v>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="n">
-        <v>0.105</v>
+        <v>0.395</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -16334,10 +16310,10 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T127" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -16346,7 +16322,7 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X127" t="n">
         <v>0</v>
@@ -16358,7 +16334,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Lucchesi</t>
+          <t>Palma</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -16368,11 +16344,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
         <v>11</v>
@@ -16386,7 +16362,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>11</v>
+        <v>14.9</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -16394,20 +16370,20 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -16419,10 +16395,10 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T128" t="n">
-        <v>5.33</v>
+        <v>6.5</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -16443,24 +16419,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Helland</t>
+          <t>Lucchesi</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E129" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F129" t="n">
         <v>6</v>
@@ -16471,7 +16447,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -16479,20 +16455,20 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
         <v>1</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -16504,10 +16480,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T129" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -16516,7 +16492,7 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X129" t="n">
         <v>0</v>
@@ -16528,7 +16504,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Abankwah</t>
+          <t>Helland</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -16538,17 +16514,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D130" t="n">
         <v>3</v>
       </c>
       <c r="E130" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
@@ -16556,7 +16532,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>8.6</v>
+        <v>9.9</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -16564,22 +16540,20 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K130" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="L130" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
-      </c>
-      <c r="N130" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
-        <v>0.026</v>
+        <v>0.158</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -16591,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T130" t="n">
         <v>6</v>
@@ -16603,7 +16577,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X130" t="n">
         <v>0</v>
@@ -16615,48 +16589,70 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kofler</t>
+          <t>Abankwah</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="n">
+        <v>10</v>
+      </c>
+      <c r="F131" t="n">
+        <v>5</v>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>2</v>
+      </c>
+      <c r="K131" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L131" t="n">
         <v>6</v>
       </c>
-      <c r="E131" t="n">
-        <v>8</v>
-      </c>
-      <c r="F131" t="n">
-        <v>4</v>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N131" t="n">
+        <v>6</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
       <c r="S131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T131" t="n">
         <v>6</v>
@@ -16667,8 +16663,12 @@
       <c r="V131" t="n">
         <v>0</v>
       </c>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+      <c r="W131" t="n">
+        <v>1</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr"/>
@@ -16676,27 +16676,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Leysen F.</t>
+          <t>Kofler</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>6</v>
       </c>
       <c r="E132" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F132" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
@@ -16717,16 +16717,16 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T132" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr"/>
@@ -16737,24 +16737,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Balerdi</t>
+          <t>Leysen F.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>6</v>
       </c>
       <c r="E133" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F133" t="n">
         <v>6</v>
@@ -16778,7 +16778,7 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T133" t="n">
         <v>6.5</v>
@@ -16787,7 +16787,7 @@
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
@@ -16798,7 +16798,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Caleta-Car</t>
+          <t>Balerdi</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -16839,10 +16839,10 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T134" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -16859,24 +16859,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Viery</t>
+          <t>Caleta-Car</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F135" t="n">
         <v>6</v>
@@ -16900,10 +16900,10 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -16920,17 +16920,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Correia T.</t>
+          <t>Viery</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -16964,7 +16964,7 @@
         <v>2</v>
       </c>
       <c r="T136" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -16981,17 +16981,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Patterson</t>
+          <t>Correia T.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -17022,10 +17022,10 @@
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T137" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -17042,27 +17042,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Mitaj</t>
+          <t>Patterson</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E138" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
@@ -17083,10 +17083,10 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -17103,17 +17103,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Halhal</t>
+          <t>Mitaj</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -17144,10 +17144,10 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -17164,27 +17164,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Favasuli</t>
+          <t>Halhal</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>3</v>
       </c>
       <c r="E140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
@@ -17205,10 +17205,10 @@
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -17225,27 +17225,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Lulli</t>
+          <t>Favasuli</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>3</v>
       </c>
       <c r="E141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
@@ -17266,10 +17266,10 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -17286,17 +17286,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Drameh</t>
+          <t>Lulli</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -17327,10 +17327,10 @@
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -17347,68 +17347,46 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cabal</t>
+          <t>Drameh</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E143" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
-      </c>
-      <c r="G143" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J143" t="n">
-        <v>9</v>
-      </c>
-      <c r="K143" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="L143" t="n">
-        <v>6.56</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
       <c r="M143" t="n">
-        <v>3</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="P143" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
       <c r="S143" t="n">
         <v>0</v>
       </c>
@@ -17421,12 +17399,8 @@
       <c r="V143" t="n">
         <v>0</v>
       </c>
-      <c r="W143" t="n">
-        <v>1</v>
-      </c>
-      <c r="X143" t="n">
-        <v>0</v>
-      </c>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
       <c r="AA143" t="inlineStr"/>
@@ -17434,24 +17408,24 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Idrissi R.</t>
+          <t>Cabal</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F144" t="n">
         <v>2</v>
@@ -17462,7 +17436,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>62.3</v>
+        <v>65.2</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -17470,20 +17444,22 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K144" t="n">
-        <v>5.82</v>
+        <v>5.94</v>
       </c>
       <c r="L144" t="n">
-        <v>6.09</v>
+        <v>6.56</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
-      </c>
-      <c r="N144" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.53</v>
+      </c>
       <c r="O144" t="n">
-        <v>0.447</v>
+        <v>0.298</v>
       </c>
       <c r="P144" t="n">
         <v>2</v>
@@ -17507,7 +17483,7 @@
         <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X144" t="n">
         <v>0</v>
@@ -17519,24 +17495,24 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>De Silvestri</t>
+          <t>Idrissi R.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F145" t="n">
         <v>2</v>
@@ -17547,7 +17523,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>50.2</v>
+        <v>62.3</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -17555,25 +17531,23 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K145" t="n">
-        <v>6.05</v>
+        <v>5.82</v>
       </c>
       <c r="L145" t="n">
-        <v>5.95</v>
+        <v>6.09</v>
       </c>
       <c r="M145" t="n">
-        <v>3</v>
-      </c>
-      <c r="N145" t="n">
-        <v>-0.34</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="n">
-        <v>0.333</v>
+        <v>0.447</v>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
@@ -17594,7 +17568,7 @@
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X145" t="n">
         <v>0</v>
@@ -17606,27 +17580,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Pellegrini Lu.</t>
+          <t>De Silvestri</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D146" t="n">
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G146" s="6" t="inlineStr">
         <is>
@@ -17634,7 +17608,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>47.8</v>
+        <v>50.2</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -17642,25 +17616,25 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K146" t="n">
-        <v>5.85</v>
+        <v>6.05</v>
       </c>
       <c r="L146" t="n">
-        <v>5.81</v>
+        <v>5.95</v>
       </c>
       <c r="M146" t="n">
         <v>3</v>
       </c>
       <c r="N146" t="n">
-        <v>-0.17</v>
+        <v>-0.34</v>
       </c>
       <c r="O146" t="n">
-        <v>0.526</v>
+        <v>0.333</v>
       </c>
       <c r="P146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
         <v>0</v>
@@ -17681,7 +17655,7 @@
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -17693,21 +17667,21 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sverko</t>
+          <t>Pellegrini Lu.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
         <v>7</v>
@@ -17721,7 +17695,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -17729,20 +17703,22 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K147" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="L147" t="n">
-        <v>5.86</v>
+        <v>5.81</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
-      </c>
-      <c r="N147" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-0.17</v>
+      </c>
       <c r="O147" t="n">
-        <v>0.368</v>
+        <v>0.526</v>
       </c>
       <c r="P147" t="n">
         <v>1</v>
@@ -17766,7 +17742,7 @@
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -17778,35 +17754,35 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Terracciano F.</t>
+          <t>Sverko</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B;Dd;Ds</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
+        <v>7</v>
+      </c>
+      <c r="F148" t="n">
         <v>4</v>
       </c>
-      <c r="F148" t="n">
-        <v>2</v>
-      </c>
       <c r="G148" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -17814,25 +17790,23 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K148" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L148" t="n">
         <v>5.86</v>
       </c>
-      <c r="L148" t="n">
-        <v>5.83</v>
-      </c>
       <c r="M148" t="n">
-        <v>3</v>
-      </c>
-      <c r="N148" t="n">
-        <v>0.14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="n">
-        <v>0.535</v>
+        <v>0.368</v>
       </c>
       <c r="P148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
@@ -17853,7 +17827,7 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -17865,24 +17839,24 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Biraghi</t>
+          <t>Terracciano F.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>B;Dd;Ds</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D149" t="n">
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F149" t="n">
         <v>2</v>
@@ -17893,7 +17867,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>35.2</v>
+        <v>42.6</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -17901,25 +17875,25 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K149" t="n">
-        <v>5.59</v>
+        <v>5.86</v>
       </c>
       <c r="L149" t="n">
-        <v>5.59</v>
+        <v>5.83</v>
       </c>
       <c r="M149" t="n">
         <v>3</v>
       </c>
       <c r="N149" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="O149" t="n">
-        <v>0.526</v>
+        <v>0.535</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q149" t="n">
         <v>0</v>
@@ -17940,7 +17914,7 @@
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -17952,17 +17926,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Lazzari</t>
+          <t>Biraghi</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -17980,7 +17954,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>32</v>
+        <v>35.2</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -17988,22 +17962,22 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K150" t="n">
-        <v>5.79</v>
+        <v>5.59</v>
       </c>
       <c r="L150" t="n">
-        <v>5.74</v>
+        <v>5.59</v>
       </c>
       <c r="M150" t="n">
         <v>3</v>
       </c>
       <c r="N150" t="n">
-        <v>-0.13</v>
+        <v>-0.36</v>
       </c>
       <c r="O150" t="n">
-        <v>0.553</v>
+        <v>0.526</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -18027,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -18039,27 +18013,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Pongracic</t>
+          <t>Lazzari</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
@@ -18067,30 +18041,30 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>29.1</v>
+        <v>32</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="K151" t="n">
-        <v>5.84</v>
+        <v>5.79</v>
       </c>
       <c r="L151" t="n">
-        <v>5.67</v>
+        <v>5.74</v>
       </c>
       <c r="M151" t="n">
         <v>3</v>
       </c>
       <c r="N151" t="n">
-        <v>-0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="O151" t="n">
-        <v>0.772</v>
+        <v>0.553</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
@@ -18102,10 +18076,10 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -18114,7 +18088,7 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="X151" t="n">
         <v>0</v>
@@ -18126,74 +18100,74 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ebosse</t>
+          <t>Pongracic</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>3</v>
       </c>
       <c r="E152" t="n">
+        <v>8</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4</v>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>35</v>
+      </c>
+      <c r="K152" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="L152" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M152" t="n">
+        <v>3</v>
+      </c>
+      <c r="N152" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>1</v>
+      </c>
+      <c r="T152" t="n">
         <v>5</v>
       </c>
-      <c r="F152" t="n">
-        <v>2</v>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J152" t="n">
-        <v>16</v>
-      </c>
-      <c r="K152" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L152" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="M152" t="n">
-        <v>3</v>
-      </c>
-      <c r="N152" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O152" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>1</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="n">
-        <v>3</v>
-      </c>
-      <c r="T152" t="n">
-        <v>5.83</v>
-      </c>
       <c r="U152" t="n">
         <v>0</v>
       </c>
@@ -18201,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="X152" t="n">
         <v>0</v>
@@ -18213,21 +18187,21 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sabelli</t>
+          <t>Ebosse</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E153" t="n">
         <v>5</v>
@@ -18249,37 +18223,37 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K153" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="L153" t="n">
-        <v>5.65</v>
+        <v>5.72</v>
       </c>
       <c r="M153" t="n">
         <v>3</v>
       </c>
       <c r="N153" t="n">
-        <v>-0.24</v>
+        <v>2.44</v>
       </c>
       <c r="O153" t="n">
-        <v>0.649</v>
+        <v>0.158</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T153" t="n">
-        <v>5</v>
+        <v>5.83</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -18288,7 +18262,7 @@
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X153" t="n">
         <v>0</v>
@@ -18300,24 +18274,24 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Marianucci</t>
+          <t>Sabelli</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F154" t="n">
         <v>2</v>
@@ -18328,45 +18302,45 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>25.8</v>
+        <v>28.2</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K154" t="n">
-        <v>5.73</v>
+        <v>5.81</v>
       </c>
       <c r="L154" t="n">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="O154" t="n">
-        <v>0.316</v>
+        <v>0.649</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -18375,7 +18349,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X154" t="n">
         <v>0</v>
@@ -18387,27 +18361,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Arizala</t>
+          <t>Marianucci</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F155" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
@@ -18415,34 +18389,36 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K155" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="L155" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
-      </c>
-      <c r="N155" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
       <c r="O155" t="n">
-        <v>0.132</v>
+        <v>0.316</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -18460,7 +18436,7 @@
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X155" t="n">
         <v>0</v>
@@ -18472,27 +18448,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Rugani</t>
+          <t>Arizala</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
@@ -18500,30 +18476,28 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K156" t="n">
-        <v>5.69</v>
+        <v>5.8</v>
       </c>
       <c r="L156" t="n">
-        <v>5.56</v>
+        <v>5.8</v>
       </c>
       <c r="M156" t="n">
-        <v>3</v>
-      </c>
-      <c r="N156" t="n">
-        <v>3.14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="n">
-        <v>0.193</v>
+        <v>0.132</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -18547,7 +18521,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X156" t="n">
         <v>0</v>
@@ -18559,7 +18533,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Marin R.</t>
+          <t>Rugani</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -18569,46 +18543,48 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
+        <v>3</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
         <v>8</v>
       </c>
-      <c r="F157" t="n">
-        <v>4</v>
-      </c>
-      <c r="G157" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H157" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J157" t="n">
-        <v>3</v>
-      </c>
       <c r="K157" t="n">
-        <v>6</v>
+        <v>5.69</v>
       </c>
       <c r="L157" t="n">
-        <v>5.83</v>
+        <v>5.56</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
-      </c>
-      <c r="N157" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N157" t="n">
+        <v>3.14</v>
+      </c>
       <c r="O157" t="n">
-        <v>0.079</v>
+        <v>0.193</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -18620,10 +18596,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -18632,7 +18608,7 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X157" t="n">
         <v>0</v>
@@ -18644,7 +18620,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ziolkowski</t>
+          <t>Marin R.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -18654,11 +18630,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" t="n">
         <v>8</v>
@@ -18672,7 +18648,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>21.3</v>
+        <v>23.9</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -18680,20 +18656,20 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K158" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="L158" t="n">
-        <v>5.78</v>
+        <v>5.83</v>
       </c>
       <c r="M158" t="n">
         <v>1</v>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="n">
-        <v>0.237</v>
+        <v>0.079</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -18705,10 +18681,10 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T158" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>
@@ -18717,7 +18693,7 @@
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X158" t="n">
         <v>0</v>
@@ -18729,24 +18705,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Candè</t>
+          <t>Ziolkowski</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F159" t="n">
         <v>4</v>
@@ -18757,7 +18733,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>18.8</v>
+        <v>21.3</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -18765,22 +18741,20 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K159" t="n">
-        <v>5.69</v>
+        <v>5.94</v>
       </c>
       <c r="L159" t="n">
-        <v>5.56</v>
+        <v>5.78</v>
       </c>
       <c r="M159" t="n">
-        <v>2</v>
-      </c>
-      <c r="N159" t="n">
-        <v>-0.26</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="n">
-        <v>0.329</v>
+        <v>0.237</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -18804,7 +18778,7 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X159" t="n">
         <v>0</v>
@@ -18816,27 +18790,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Casale</t>
+          <t>Candè</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D160" t="n">
         <v>2</v>
       </c>
       <c r="E160" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
@@ -18844,7 +18818,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -18852,22 +18826,22 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K160" t="n">
-        <v>5.65</v>
+        <v>5.69</v>
       </c>
       <c r="L160" t="n">
-        <v>5.65</v>
+        <v>5.56</v>
       </c>
       <c r="M160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N160" t="n">
-        <v>0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="O160" t="n">
-        <v>0.386</v>
+        <v>0.329</v>
       </c>
       <c r="P160" t="n">
         <v>0</v>
@@ -18891,7 +18865,7 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X160" t="n">
         <v>0</v>
@@ -18903,7 +18877,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Casale</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -18913,14 +18887,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F161" t="n">
         <v>2</v>
@@ -18931,7 +18905,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -18939,22 +18913,22 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K161" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="L161" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="M161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N161" t="n">
-        <v>-0.05</v>
+        <v>0.11</v>
       </c>
       <c r="O161" t="n">
-        <v>0.303</v>
+        <v>0.386</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -18978,7 +18952,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X161" t="n">
         <v>0</v>
@@ -18990,58 +18964,58 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Goglichidze</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
+        <v>4</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
         <v>5</v>
       </c>
-      <c r="F162" t="n">
-        <v>2</v>
-      </c>
-      <c r="G162" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J162" t="n">
-        <v>6</v>
-      </c>
       <c r="K162" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="L162" t="n">
-        <v>5.58</v>
+        <v>5.7</v>
       </c>
       <c r="M162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N162" t="n">
-        <v>2.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O162" t="n">
-        <v>0.342</v>
+        <v>0.303</v>
       </c>
       <c r="P162" t="n">
         <v>0</v>
@@ -19065,7 +19039,7 @@
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X162" t="n">
         <v>0</v>
@@ -19077,56 +19051,58 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Moreno M.</t>
+          <t>Goglichidze</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E163" t="n">
+        <v>5</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
         <v>6</v>
       </c>
-      <c r="F163" t="n">
-        <v>3</v>
-      </c>
-      <c r="G163" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H163" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
       <c r="K163" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="L163" t="n">
-        <v>5.67</v>
+        <v>5.58</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
-      </c>
-      <c r="N163" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2.01</v>
+      </c>
       <c r="O163" t="n">
-        <v>0.079</v>
+        <v>0.342</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -19138,10 +19114,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T163" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -19150,7 +19126,7 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X163" t="n">
         <v>0</v>
@@ -19162,27 +19138,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ndaba</t>
+          <t>Moreno M.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
@@ -19190,7 +19166,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -19198,20 +19174,20 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K164" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L164" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M164" t="n">
         <v>1</v>
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="n">
-        <v>0.237</v>
+        <v>0.079</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -19223,10 +19199,10 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T164" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U164" t="n">
         <v>0</v>
@@ -19247,7 +19223,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Carboni F.</t>
+          <t>Ndaba</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -19257,14 +19233,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D165" t="n">
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F165" t="n">
         <v>2</v>
@@ -19275,7 +19251,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -19283,22 +19259,20 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K165" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L165" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M165" t="n">
-        <v>3</v>
-      </c>
-      <c r="N165" t="n">
-        <v>2.44</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="n">
-        <v>0.061</v>
+        <v>0.237</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -19310,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T165" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -19334,12 +19308,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ndiaye</t>
+          <t>Carboni F.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -19351,10 +19325,10 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
@@ -19362,7 +19336,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>11.7</v>
+        <v>14.1</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -19370,20 +19344,22 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>5.59</v>
+        <v>6</v>
       </c>
       <c r="L166" t="n">
-        <v>5.36</v>
+        <v>6</v>
       </c>
       <c r="M166" t="n">
-        <v>1</v>
-      </c>
-      <c r="N166" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2.44</v>
+      </c>
       <c r="O166" t="n">
-        <v>0.289</v>
+        <v>0.061</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -19395,10 +19371,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -19407,10 +19383,10 @@
         <v>0</v>
       </c>
       <c r="W166" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y166" t="inlineStr"/>
       <c r="Z166" t="inlineStr"/>
@@ -19419,7 +19395,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Odenthal</t>
+          <t>Ndiaye</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -19429,11 +19405,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
         <v>8</v>
@@ -19447,28 +19423,28 @@
         </is>
       </c>
       <c r="H167" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
         <v>11</v>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J167" t="n">
-        <v>0</v>
-      </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="M167" t="n">
         <v>1</v>
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="P167" t="n">
         <v>0</v>
@@ -19483,19 +19459,19 @@
         <v>1</v>
       </c>
       <c r="T167" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y167" t="inlineStr"/>
       <c r="Z167" t="inlineStr"/>
@@ -19504,7 +19480,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Otoa</t>
+          <t>Odenthal</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -19514,17 +19490,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E168" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
@@ -19532,7 +19508,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -19540,46 +19516,44 @@
         </is>
       </c>
       <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>1</v>
+      </c>
+      <c r="T168" t="n">
         <v>10</v>
       </c>
-      <c r="K168" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L168" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="M168" t="n">
-        <v>2</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="O168" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
-      </c>
-      <c r="S168" t="n">
-        <v>1</v>
-      </c>
-      <c r="T168" t="n">
-        <v>4.5</v>
-      </c>
       <c r="U168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
       </c>
       <c r="W168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X168" t="n">
         <v>0</v>
@@ -19591,24 +19565,24 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sagrado</t>
+          <t>Otoa</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F169" t="n">
         <v>2</v>
@@ -19619,7 +19593,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -19627,20 +19601,22 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K169" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L169" t="n">
-        <v>5.33</v>
+        <v>5.35</v>
       </c>
       <c r="M169" t="n">
-        <v>1</v>
-      </c>
-      <c r="N169" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0.68</v>
+      </c>
       <c r="O169" t="n">
-        <v>0.079</v>
+        <v>0.171</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -19655,10 +19631,10 @@
         <v>1</v>
       </c>
       <c r="T169" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="U169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -19676,60 +19652,84 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Terzic</t>
+          <t>Sagrado</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D170" t="n">
         <v>4</v>
       </c>
       <c r="E170" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
+      <c r="H170" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L170" t="n">
+        <v>5.33</v>
+      </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr"/>
+      <c r="O170" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
       <c r="S170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T170" t="n">
-        <v>5.75</v>
+        <v>10</v>
       </c>
       <c r="U170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
       </c>
-      <c r="W170" t="inlineStr"/>
-      <c r="X170" t="inlineStr"/>
+      <c r="W170" t="n">
+        <v>1</v>
+      </c>
+      <c r="X170" t="n">
+        <v>0</v>
+      </c>
       <c r="Y170" t="inlineStr"/>
       <c r="Z170" t="inlineStr"/>
       <c r="AA170" t="inlineStr"/>
@@ -19737,27 +19737,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Cinquegrano</t>
+          <t>Terzic</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>4</v>
       </c>
       <c r="E171" t="n">
+        <v>8</v>
+      </c>
+      <c r="F171" t="n">
         <v>4</v>
-      </c>
-      <c r="F171" t="n">
-        <v>2</v>
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
@@ -19778,16 +19778,16 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T171" t="n">
-        <v>6.33</v>
+        <v>5.75</v>
       </c>
       <c r="U171" t="n">
         <v>0</v>
       </c>
       <c r="V171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W171" t="inlineStr"/>
       <c r="X171" t="inlineStr"/>
@@ -19798,7 +19798,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Tchato</t>
+          <t>Cinquegrano</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -19808,17 +19808,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E172" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
@@ -19839,16 +19839,16 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T172" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="U172" t="n">
         <v>0</v>
       </c>
       <c r="V172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W172" t="inlineStr"/>
       <c r="X172" t="inlineStr"/>
@@ -19859,17 +19859,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Kambwala</t>
+          <t>Tchato</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -19920,27 +19920,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Alhassane</t>
+          <t>Kambwala</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E174" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
@@ -19961,10 +19961,10 @@
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -19981,17 +19981,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Akpoguma</t>
+          <t>Alhassane</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -20022,10 +20022,10 @@
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T175" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U175" t="n">
         <v>0</v>
@@ -20042,27 +20042,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Franjic</t>
+          <t>Akpoguma</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D176" t="n">
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
@@ -20083,10 +20083,10 @@
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T176" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -20103,27 +20103,27 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Puczka</t>
+          <t>Franjic</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G177" s="6" t="inlineStr">
         <is>
@@ -20144,10 +20144,10 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T177" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U177" t="n">
         <v>0</v>
@@ -20164,24 +20164,24 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Diawara S.</t>
+          <t>Puczka</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D178" t="n">
         <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F178" t="n">
         <v>2</v>
@@ -20225,17 +20225,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Bakoune</t>
+          <t>Diawara S.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -20266,10 +20266,10 @@
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T179" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U179" t="n">
         <v>0</v>
@@ -20286,24 +20286,24 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Aurelio</t>
+          <t>Bakoune</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D180" t="n">
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F180" t="n">
         <v>2</v>
@@ -20327,10 +20327,10 @@
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T180" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U180" t="n">
         <v>0</v>
@@ -20347,68 +20347,46 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Dembelè A.</t>
+          <t>Aurelio</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D181" t="n">
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H181" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J181" t="n">
-        <v>1</v>
-      </c>
-      <c r="K181" t="n">
-        <v>5</v>
-      </c>
-      <c r="L181" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
       <c r="M181" t="n">
-        <v>2</v>
-      </c>
-      <c r="N181" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="O181" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
       <c r="S181" t="n">
         <v>0</v>
       </c>
@@ -20421,12 +20399,8 @@
       <c r="V181" t="n">
         <v>0</v>
       </c>
-      <c r="W181" t="n">
-        <v>0</v>
-      </c>
-      <c r="X181" t="n">
-        <v>0</v>
-      </c>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr"/>
       <c r="Z181" t="inlineStr"/>
       <c r="AA181" t="inlineStr"/>
@@ -20434,24 +20408,24 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Patric</t>
+          <t>Dembelè A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F182" t="n">
         <v>1</v>
@@ -20462,7 +20436,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>38.1</v>
+        <v>43.8</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -20470,22 +20444,22 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K182" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="L182" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="M182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N182" t="n">
-        <v>-0.28</v>
+        <v>-0.89</v>
       </c>
       <c r="O182" t="n">
-        <v>0.325</v>
+        <v>0.132</v>
       </c>
       <c r="P182" t="n">
         <v>0</v>
@@ -20509,7 +20483,7 @@
         <v>0</v>
       </c>
       <c r="W182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X182" t="n">
         <v>0</v>
@@ -20521,17 +20495,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Goldaniga</t>
+          <t>Patric</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -20549,7 +20523,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>27.1</v>
+        <v>38.1</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -20557,22 +20531,22 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M183" t="n">
         <v>3</v>
       </c>
       <c r="N183" t="n">
-        <v>-5.66</v>
+        <v>-0.28</v>
       </c>
       <c r="O183" t="n">
-        <v>0.377</v>
+        <v>0.325</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
@@ -20596,7 +20570,7 @@
         <v>0</v>
       </c>
       <c r="W183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X183" t="n">
         <v>0</v>
@@ -20608,7 +20582,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Amey</t>
+          <t>Goldaniga</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -20618,7 +20592,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -20636,11 +20610,11 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>11</v>
+        <v>27.1</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -20653,11 +20627,13 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>1</v>
-      </c>
-      <c r="N184" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N184" t="n">
+        <v>-5.66</v>
+      </c>
       <c r="O184" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
@@ -20693,7 +20669,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Antov</t>
+          <t>Amey</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -20703,14 +20679,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D185" t="n">
         <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
         <v>1</v>
@@ -20778,24 +20754,24 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Pieragnolo</t>
+          <t>Antov</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D186" t="n">
         <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F186" t="n">
         <v>1</v>
@@ -20863,21 +20839,21 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Drobnic</t>
+          <t>Pieragnolo</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" t="n">
         <v>1</v>
@@ -20890,24 +20866,44 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
+      <c r="H187" t="n">
+        <v>11</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr"/>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
       <c r="S187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T187" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U187" t="n">
         <v>0</v>
@@ -20915,8 +20911,12 @@
       <c r="V187" t="n">
         <v>0</v>
       </c>
-      <c r="W187" t="inlineStr"/>
-      <c r="X187" t="inlineStr"/>
+      <c r="W187" t="n">
+        <v>0</v>
+      </c>
+      <c r="X187" t="n">
+        <v>0</v>
+      </c>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="inlineStr"/>
       <c r="AA187" t="inlineStr"/>
@@ -20924,21 +20924,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Drobnic</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
         <v>1</v>
@@ -20965,10 +20965,10 @@
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
@@ -20985,17 +20985,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Omar Fayed</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -21046,17 +21046,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Maye</t>
+          <t>Omar Fayed</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -21104,8 +21104,69 @@
       <c r="Z190" t="inlineStr"/>
       <c r="AA190" t="inlineStr"/>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Maye</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ds;Dc</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="n">
+        <v>0</v>
+      </c>
+      <c r="V191" t="n">
+        <v>0</v>
+      </c>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="inlineStr"/>
+      <c r="Z191" t="inlineStr"/>
+      <c r="AA191" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA190"/>
+  <autoFilter ref="A1:AA191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Attaccanti" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$191</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$193</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$87</definedName>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA65"/>
+  <dimension ref="A1:AA64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>70.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>71.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>69.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>68.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>59.2</v>
+        <v>58.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Muric</t>
+          <t>Perri</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1756,61 +1756,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
           <t>1a Fascia</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4.77</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1818,12 +1798,8 @@
       <c r="V15" t="n">
         <v>0</v>
       </c>
-      <c r="W15" t="n">
-        <v>43</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -1831,7 +1807,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Perri</t>
+          <t>Sanchez Ro.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1841,17 +1817,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -1872,10 +1848,10 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1892,7 +1868,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sanchez Ro.</t>
+          <t>Milinkovic-Savic V.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1902,36 +1878,58 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>1a Fascia</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>27</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.65</v>
+      </c>
       <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
@@ -1944,8 +1942,12 @@
       <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>24</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -1953,7 +1955,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Milinkovic-Savic V.</t>
+          <t>Pessina Mas.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1963,48 +1965,46 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>27</v>
-      </c>
       <c r="K18" t="n">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="L18" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.28</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>0.877</v>
+        <v>0.105</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
@@ -2040,7 +2040,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pessina Mas.</t>
+          <t>Provedel</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -2068,28 +2068,30 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>68.8</v>
+        <v>63.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>6.12</v>
+        <v>6.26</v>
       </c>
       <c r="L19" t="n">
-        <v>5.62</v>
+        <v>5.35</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.59</v>
+      </c>
       <c r="O19" t="n">
-        <v>0.105</v>
+        <v>0.754</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2113,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
@@ -2125,7 +2127,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Provedel</t>
+          <t>Stankovic F.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2135,17 +2137,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -2153,7 +2155,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>63.6</v>
+        <v>61.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2161,22 +2163,22 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>6.26</v>
+        <v>6.6</v>
       </c>
       <c r="L20" t="n">
-        <v>5.35</v>
+        <v>5.23</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.59</v>
+        <v>5.23</v>
       </c>
       <c r="O20" t="n">
-        <v>0.754</v>
+        <v>0.197</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2188,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2200,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="X20" t="n">
         <v>1</v>
@@ -2212,7 +2214,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stankovic F.</t>
+          <t>Muric</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2222,17 +2224,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -2240,30 +2242,28 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>61.7</v>
+        <v>57.1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>6.6</v>
+        <v>6.08</v>
       </c>
       <c r="L21" t="n">
-        <v>5.23</v>
+        <v>4.77</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.23</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>0.197</v>
+        <v>0.842</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.67</v>
+        <v>4.33</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>56</v>
+        <v>55.7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Christensen O.</t>
+          <t>Sportiello</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>42.3</v>
+        <v>36.8</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2510,19 +2510,19 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.28</v>
+        <v>-0.34</v>
       </c>
       <c r="O24" t="n">
-        <v>0.044</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sportiello</t>
+          <t>Sherri</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>37.6</v>
+        <v>34.1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2594,22 +2594,22 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.34</v>
+        <v>-4.29</v>
       </c>
       <c r="O25" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sherri</t>
+          <t>Palmisani</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
@@ -2673,11 +2673,11 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>34.9</v>
+        <v>30.8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -2690,13 +2690,11 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-4.29</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2708,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2732,7 +2730,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Palmisani</t>
+          <t>Tornqvist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2742,25 +2740,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="n">
-        <v>12</v>
-      </c>
-      <c r="F27" t="n">
-        <v>6</v>
-      </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2793,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2817,7 +2815,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tornqvist</t>
+          <t>Vigorito</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2827,17 +2825,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
@@ -2845,11 +2843,11 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2862,9 +2860,11 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
@@ -2902,7 +2902,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vigorito</t>
+          <t>Daffara</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2912,58 +2912,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
         <v>0</v>
       </c>
@@ -2976,12 +2954,8 @@
       <c r="V29" t="n">
         <v>0</v>
       </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -2989,7 +2963,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Daffara</t>
+          <t>Thiam</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2999,17 +2973,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
@@ -3030,10 +3004,10 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3050,7 +3024,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Thiam</t>
+          <t>Happonen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3060,17 +3034,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
@@ -3091,10 +3065,10 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3111,7 +3085,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Happonen</t>
+          <t>Mascardi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3121,17 +3095,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
@@ -3152,10 +3126,10 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3172,7 +3146,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mascardi</t>
+          <t>Terracciano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3182,41 +3156,63 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6</v>
+      </c>
       <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3224,8 +3220,12 @@
       <c r="V33" t="n">
         <v>0</v>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Terracciano</t>
+          <t>Motta</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>73.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3269,22 +3269,20 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
         <v>6</v>
       </c>
       <c r="L34" t="n">
-        <v>6</v>
+        <v>5.17</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>0.333</v>
+        <v>0.237</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3308,10 +3306,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
@@ -3320,7 +3318,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Motta</t>
+          <t>Turati</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3330,7 +3328,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -3348,7 +3346,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>63.2</v>
+        <v>53.2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3356,20 +3354,22 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="L35" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.37</v>
+      </c>
       <c r="O35" t="n">
-        <v>0.237</v>
+        <v>0.588</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3393,10 +3393,10 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
@@ -3405,7 +3405,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Turati</t>
+          <t>Christensen O.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -3433,30 +3433,30 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>53.8</v>
+        <v>41.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>6.17</v>
+        <v>7.5</v>
       </c>
       <c r="L36" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="M36" t="n">
         <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>0.37</v>
+        <v>5.28</v>
       </c>
       <c r="O36" t="n">
-        <v>0.588</v>
+        <v>0.044</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3492,7 +3492,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Padelli</t>
+          <t>Pinsoglio</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -3520,30 +3520,30 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>48.2</v>
+        <v>41.4</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.19</v>
+        <v>-2.44</v>
       </c>
       <c r="O37" t="n">
-        <v>0.026</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pinsoglio</t>
+          <t>Contini</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>42.3</v>
+        <v>40.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>-2.44</v>
+        <v>-2.25</v>
       </c>
       <c r="O38" t="n">
         <v>0.008999999999999999</v>
@@ -3666,7 +3666,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Contini</t>
+          <t>Di Gennaro</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>41.4</v>
+        <v>40</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3702,22 +3702,22 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M39" t="n">
         <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>-2.25</v>
+        <v>2.56</v>
       </c>
       <c r="O39" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Di Gennaro</t>
+          <t>Gollini</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3789,22 +3789,22 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.56</v>
+        <v>-4.37</v>
       </c>
       <c r="O40" t="n">
-        <v>0.018</v>
+        <v>0.123</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3840,7 +3840,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gollini</t>
+          <t>Lezzerini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>40</v>
+        <v>30.8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3885,13 +3885,11 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-4.37</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -3927,7 +3925,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sommariva</t>
+          <t>Stolz</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3955,7 +3953,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3963,22 +3961,22 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -4002,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -4014,7 +4012,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lezzerini</t>
+          <t>Torriani</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4024,7 +4022,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -4042,7 +4040,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4059,9 +4057,11 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
@@ -4099,7 +4099,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Stolz</t>
+          <t>De Marzi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4144,11 +4144,9 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
         <v>0</v>
       </c>
@@ -4186,7 +4184,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Torriani</t>
+          <t>Russo A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4196,7 +4194,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -4214,7 +4212,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4231,11 +4229,9 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
         <v>0</v>
       </c>
@@ -4273,7 +4269,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>De Marzi</t>
+          <t>Siviero</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4283,7 +4279,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -4301,7 +4297,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4358,7 +4354,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Russo A.</t>
+          <t>Sommariva</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4368,7 +4364,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4386,7 +4382,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>31.3</v>
+        <v>30.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4394,20 +4390,22 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4431,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -4443,7 +4441,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Siviero</t>
+          <t>Desplanches</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4453,7 +4451,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -4470,39 +4468,19 @@
           <t>3a Fascia</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
         <v>0</v>
       </c>
@@ -4515,12 +4493,8 @@
       <c r="V48" t="n">
         <v>0</v>
       </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
@@ -4528,7 +4502,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Desplanches</t>
+          <t>Lolic</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4589,7 +4563,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lolic</t>
+          <t>Renzetti</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4599,7 +4573,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -4650,7 +4624,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Renzetti</t>
+          <t>Strajnar</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4660,7 +4634,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -4711,7 +4685,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Strajnar</t>
+          <t>Montipò</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4721,7 +4695,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -4733,24 +4707,46 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>35</v>
+      </c>
+      <c r="K52" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4.94</v>
+      </c>
       <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
@@ -4763,8 +4759,12 @@
       <c r="V52" t="n">
         <v>0</v>
       </c>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
+      <c r="W52" t="n">
+        <v>54</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3</v>
+      </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
@@ -4772,7 +4772,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Montipò</t>
+          <t>Padelli</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>62.8</v>
+        <v>47.6</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4808,28 +4808,28 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="L53" t="n">
-        <v>4.94</v>
+        <v>5.25</v>
       </c>
       <c r="M53" t="n">
         <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>0.29</v>
+        <v>1.19</v>
       </c>
       <c r="O53" t="n">
-        <v>0.947</v>
+        <v>0.026</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -4847,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="X53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>33.4</v>
+        <v>32.6</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Piana</t>
+          <t>Grandi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4991,11 +4991,9 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
         <v>0</v>
       </c>
@@ -5033,7 +5031,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Grandi</t>
+          <t>Satalino</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5043,7 +5041,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -5061,7 +5059,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5118,7 +5116,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Satalino</t>
+          <t>Bleve</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5128,7 +5126,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -5146,7 +5144,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5203,7 +5201,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bleve</t>
+          <t>Pozzi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5213,7 +5211,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -5230,39 +5228,19 @@
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
         <v>0</v>
       </c>
@@ -5275,12 +5253,8 @@
       <c r="V58" t="n">
         <v>0</v>
       </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
@@ -5288,7 +5262,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pozzi</t>
+          <t>Penev</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5298,7 +5272,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -5349,7 +5323,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Penev</t>
+          <t>Pisseri</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5359,7 +5333,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -5410,7 +5384,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pisseri</t>
+          <t>Grabara</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5420,7 +5394,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -5471,7 +5445,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Grabara</t>
+          <t>Mrozek</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5481,7 +5455,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -5493,9 +5467,9 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -5532,7 +5506,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mrozek</t>
+          <t>Ghidotti</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5542,7 +5516,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -5593,7 +5567,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ghidotti</t>
+          <t>Pompei</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5603,7 +5577,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -5651,69 +5625,8 @@
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Pompei</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Por</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AA65"/>
+  <autoFilter ref="A1:AA64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39665,7 +39578,7 @@
         <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>6.67</v>
+        <v>6.83</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$191</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$194</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21090,7 +21090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA193"/>
+  <dimension ref="A1:AA194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35482,27 +35482,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Aboukhlal</t>
+          <t>Forson O.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -35518,20 +35518,20 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K174" t="n">
-        <v>5.77</v>
+        <v>5.67</v>
       </c>
       <c r="L174" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="M174" t="n">
         <v>1</v>
       </c>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="n">
-        <v>0.289</v>
+        <v>0.158</v>
       </c>
       <c r="P174" t="n">
         <v>0</v>
@@ -35546,7 +35546,7 @@
         <v>2</v>
       </c>
       <c r="T174" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -35555,7 +35555,7 @@
         <v>0</v>
       </c>
       <c r="W174" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X174" t="n">
         <v>0</v>
@@ -35567,21 +35567,21 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Hasa</t>
+          <t>Aboukhlal</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E175" t="n">
         <v>5</v>
@@ -35595,7 +35595,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -35603,20 +35603,20 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K175" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="M175" t="n">
         <v>1</v>
       </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="P175" t="n">
         <v>0</v>
@@ -35628,10 +35628,10 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T175" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U175" t="n">
         <v>0</v>
@@ -35640,7 +35640,7 @@
         <v>0</v>
       </c>
       <c r="W175" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X175" t="n">
         <v>0</v>
@@ -35652,21 +35652,21 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Przyborek</t>
+          <t>Hasa</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
         <v>5</v>
@@ -35713,10 +35713,10 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T176" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -35737,46 +35737,66 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Grillitsch</t>
+          <t>Przyborek</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F177" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G177" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
+      <c r="H177" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr"/>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
       <c r="S177" t="n">
         <v>0</v>
       </c>
@@ -35789,8 +35809,12 @@
       <c r="V177" t="n">
         <v>0</v>
       </c>
-      <c r="W177" t="inlineStr"/>
-      <c r="X177" t="inlineStr"/>
+      <c r="W177" t="n">
+        <v>0</v>
+      </c>
+      <c r="X177" t="n">
+        <v>0</v>
+      </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
@@ -35798,27 +35822,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Fernandez T.</t>
+          <t>Grillitsch</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>T;A</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D178" t="n">
         <v>4</v>
       </c>
       <c r="E178" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
@@ -35839,10 +35863,10 @@
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T178" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U178" t="n">
         <v>0</v>
@@ -35859,24 +35883,24 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Stankovic A.</t>
+          <t>Fernandez T.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>T;A</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E179" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F179" t="n">
         <v>4</v>
@@ -35900,10 +35924,10 @@
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T179" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U179" t="n">
         <v>0</v>
@@ -35920,7 +35944,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Colombo L.</t>
+          <t>Stankovic A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -35930,17 +35954,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D180" t="n">
         <v>2</v>
       </c>
       <c r="E180" t="n">
+        <v>7</v>
+      </c>
+      <c r="F180" t="n">
         <v>4</v>
-      </c>
-      <c r="F180" t="n">
-        <v>2</v>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
@@ -35961,10 +35985,10 @@
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T180" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U180" t="n">
         <v>0</v>
@@ -35981,12 +36005,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Foe Ondoa</t>
+          <t>Colombo L.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -35998,10 +36022,10 @@
         <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
@@ -36025,7 +36049,7 @@
         <v>1</v>
       </c>
       <c r="T181" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U181" t="n">
         <v>0</v>
@@ -36042,27 +36066,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Jovanovic</t>
+          <t>Foe Ondoa</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
@@ -36083,10 +36107,10 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T182" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U182" t="n">
         <v>0</v>
@@ -36103,7 +36127,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Chakvetadze</t>
+          <t>Jovanovic</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -36117,13 +36141,13 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
@@ -36164,66 +36188,46 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Liteta</t>
+          <t>Chakvetadze</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D184" t="n">
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H184" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J184" t="n">
-        <v>4</v>
-      </c>
-      <c r="K184" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L184" t="n">
-        <v>5.75</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
       <c r="M184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N184" t="inlineStr"/>
-      <c r="O184" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="P184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0</v>
-      </c>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
       <c r="S184" t="n">
         <v>0</v>
       </c>
@@ -36236,12 +36240,8 @@
       <c r="V184" t="n">
         <v>0</v>
       </c>
-      <c r="W184" t="n">
-        <v>0</v>
-      </c>
-      <c r="X184" t="n">
-        <v>0</v>
-      </c>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="inlineStr"/>
       <c r="AA184" t="inlineStr"/>
@@ -36249,21 +36249,21 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Forson O.</t>
+          <t>Liteta</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" t="n">
         <v>1</v>
@@ -36277,7 +36277,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -36285,20 +36285,20 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K185" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="L185" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="M185" t="n">
         <v>1</v>
       </c>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="n">
-        <v>0.158</v>
+        <v>0.105</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
@@ -36310,10 +36310,10 @@
         <v>0</v>
       </c>
       <c r="S185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T185" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U185" t="n">
         <v>0</v>
@@ -36867,8 +36867,69 @@
       <c r="Z193" t="inlineStr"/>
       <c r="AA193" t="inlineStr"/>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Libra</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>C;T</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA193"/>
+  <autoFilter ref="A1:AA194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -1200,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -2190,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -9149,10 +9149,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>4.67</v>
+        <v>5.12</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -11571,16 +11571,16 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T69" t="n">
-        <v>4.75</v>
+        <v>5.67</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" t="n">
         <v>1</v>
@@ -13287,13 +13287,13 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T93" t="n">
-        <v>6.33</v>
+        <v>7.12</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V93" t="n">
         <v>1</v>
@@ -13894,10 +13894,10 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T100" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -14068,16 +14068,16 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T102" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" t="n">
         <v>3</v>
@@ -16053,10 +16053,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -16223,7 +16223,7 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T127" t="n">
         <v>5</v>
@@ -16874,10 +16874,10 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T136" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -16935,10 +16935,10 @@
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T137" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -19112,7 +19112,7 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T164" t="n">
         <v>5</v>
@@ -19626,10 +19626,10 @@
         <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T170" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="U170" t="n">
         <v>1</v>
@@ -23318,10 +23318,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -24293,13 +24293,13 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>5.33</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -26602,16 +26602,16 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T65" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" t="n">
         <v>5</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T76" t="n">
-        <v>5.17</v>
+        <v>5.5</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -27731,10 +27731,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T78" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -30125,16 +30125,16 @@
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T108" t="n">
-        <v>6.17</v>
+        <v>6.5</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W108" t="n">
         <v>4</v>
@@ -30297,10 +30297,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T110" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -30817,10 +30817,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T116" t="n">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -33726,10 +33726,10 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -39290,13 +39290,13 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>6.17</v>
+        <v>7.12</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -39893,10 +39893,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="U34" t="n">
         <v>1</v>
@@ -40065,10 +40065,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -40278,13 +40278,13 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -42344,10 +42344,10 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T65" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
